--- a/R4.8/001_SISMO_VIENTO_SALVADOR_R4.8.xlsx
+++ b/R4.8/001_SISMO_VIENTO_SALVADOR_R4.8.xlsx
@@ -2326,7 +2326,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CARGAS Y SISMO F1'!$H$264:$H$563</c:f>
+              <c:f>'CARGAS Y SISMO F1'!$H$253:$H$552</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="300"/>
@@ -3235,7 +3235,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CARGAS Y SISMO F1'!$I$264:$I$563</c:f>
+              <c:f>'CARGAS Y SISMO F1'!$I$253:$I$552</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="300"/>
@@ -8433,13 +8433,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>459440</xdr:colOff>
-      <xdr:row>268</xdr:row>
+      <xdr:row>257</xdr:row>
       <xdr:rowOff>179295</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>377985</xdr:colOff>
-      <xdr:row>292</xdr:row>
+      <xdr:row>281</xdr:row>
       <xdr:rowOff>73236</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8477,13 +8477,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>143435</xdr:colOff>
-      <xdr:row>264</xdr:row>
+      <xdr:row>253</xdr:row>
       <xdr:rowOff>123265</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>179294</xdr:colOff>
-      <xdr:row>282</xdr:row>
+      <xdr:row>271</xdr:row>
       <xdr:rowOff>134471</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -10724,7 +10724,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4814D65-3072-4760-9D04-A7584A362B51}">
-  <dimension ref="B2:AM563"/>
+  <dimension ref="B2:AM552"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.109375" customWidth="1"/>
@@ -11316,7 +11316,7 @@
         <v>64</v>
       </c>
       <c r="F137" s="36">
-        <v>0.71488</v>
+        <v>0.71241</v>
       </c>
       <c r="G137" t="s">
         <v>11</v>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="F139" s="54">
         <f>P33*Q85*P55/P99*(P57/MAX(P57,MIN(F137,6*P57)))^(2/3)</f>
-        <v>0.152532343065775</v>
+        <v>0.152884703377082</v>
       </c>
     </row>
     <row r="140" spans="4:7" ht="16.5" customHeight="1"/>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F143" s="56">
         <f>MAX(F141,F139)</f>
-        <v>0.152532343065775</v>
+        <v>0.152884703377082</v>
       </c>
     </row>
     <row r="148" spans="2:25" s="39" customFormat="1"/>
@@ -11472,14 +11472,14 @@
         <v>237</v>
       </c>
       <c r="E165" s="88">
-        <v>14968.99</v>
+        <v>15017.25</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>73</v>
       </c>
       <c r="G165" s="57">
         <f>E165/1000</f>
-        <v>14.96899</v>
+        <v>15.01725</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>74</v>
@@ -11490,14 +11490,14 @@
         <v>238</v>
       </c>
       <c r="E166" s="88">
-        <v>14968.99</v>
+        <v>15017.25</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>73</v>
       </c>
       <c r="G166" s="57">
         <f>E166/1000</f>
-        <v>14.96899</v>
+        <v>15.01725</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>74</v>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="G170" s="53">
         <f>G168*G165</f>
-        <v>2.56611257142857</v>
+        <v>2.57438571428572</v>
       </c>
       <c r="H170" s="1" t="s">
         <v>74</v>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="G171" s="53">
         <f>G168*G166</f>
-        <v>2.56611257142857</v>
+        <v>2.57438571428572</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>74</v>
@@ -11663,13 +11663,13 @@
         <v>1</v>
       </c>
       <c r="C177" s="28">
-        <v>1.399</v>
+        <v>1.404</v>
       </c>
       <c r="D177" s="67">
-        <v>0.71488</v>
+        <v>0.71241</v>
       </c>
       <c r="E177" s="28">
-        <v>76.67</v>
+        <v>77.05</v>
       </c>
       <c r="F177" s="28">
         <v>0</v>
@@ -11685,15 +11685,15 @@
         <v>0.71</v>
       </c>
       <c r="J177" s="31">
-        <f>VLOOKUP(I177,$H$264:$I$563,2,0)</f>
+        <f>VLOOKUP(I177,$H$253:$I$552,2,0)</f>
         <v>0.153230472396236</v>
       </c>
       <c r="K177" s="32">
-        <f>J177*$K$234*E177/100</f>
-        <v>1758.5839370761</v>
+        <f>J177*$K$223*E177/100</f>
+        <v>1772.99779008192</v>
       </c>
       <c r="L177" s="34">
-        <f>J177*$K$235*G177/100</f>
+        <f>J177*$K$224*G177/100</f>
         <v>0</v>
       </c>
       <c r="N177" s="10" t="s">
@@ -11734,15 +11734,15 @@
         <v>0.54</v>
       </c>
       <c r="J178" s="31">
-        <f>VLOOKUP(I178,$H$264:$I$563,2,0)</f>
+        <f>VLOOKUP(I178,$H$253:$I$552,2,0)</f>
         <v>0.17142857142857146</v>
       </c>
       <c r="K178" s="32">
-        <f>J178*$K$234*E178/100</f>
+        <f>J178*$K$223*E178/100</f>
         <v>0</v>
       </c>
       <c r="L178" s="34">
-        <f>J178*$K$235*G178/100</f>
+        <f>J178*$K$224*G178/100</f>
         <v>0</v>
       </c>
       <c r="N178" s="10" t="s">
@@ -11783,15 +11783,15 @@
         <v>0.54</v>
       </c>
       <c r="J179" s="31">
-        <f t="shared" ref="J179" si="2">VLOOKUP(I179,$H$264:$I$563,2,0)</f>
+        <f t="shared" ref="J179" si="2">VLOOKUP(I179,$H$253:$I$552,2,0)</f>
         <v>0.17142857142857146</v>
       </c>
       <c r="K179" s="32">
-        <f t="shared" ref="K179" si="3">J179*$K$234*E179/100</f>
-        <v>0.513222514285714</v>
+        <f t="shared" ref="K179" si="3">J179*$K$223*E179/100</f>
+        <v>0.514877142857143</v>
       </c>
       <c r="L179" s="34">
-        <f t="shared" ref="L179" si="4">J179*$K$235*G179/100</f>
+        <f t="shared" ref="L179" si="4">J179*$K$224*G179/100</f>
         <v>0</v>
       </c>
       <c r="N179" s="10"/>
@@ -11820,19 +11820,19 @@
         <v>10</v>
       </c>
       <c r="I180" s="29">
-        <f t="shared" ref="I180:I231" si="5">ROUND(D180,2)</f>
+        <f t="shared" ref="I180:I220" si="5">ROUND(D180,2)</f>
         <v>0.5</v>
       </c>
       <c r="J180" s="31">
-        <f t="shared" ref="J180:J231" si="6">VLOOKUP(I180,$H$264:$I$563,2,0)</f>
+        <f t="shared" ref="J180:J220" si="6">VLOOKUP(I180,$H$253:$I$552,2,0)</f>
         <v>0.17142857142857146</v>
       </c>
       <c r="K180" s="32">
-        <f t="shared" ref="K180:K231" si="7">J180*$K$234*E180/100</f>
+        <f t="shared" ref="K180:K220" si="7">J180*$K$223*E180/100</f>
         <v>0</v>
       </c>
       <c r="L180" s="34">
-        <f t="shared" ref="L180:L231" si="8">J180*$K$235*G180/100</f>
+        <f t="shared" ref="L180:L220" si="8">J180*$K$224*G180/100</f>
         <v>0</v>
       </c>
       <c r="N180" s="10"/>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="K181" s="32">
         <f t="shared" si="7"/>
-        <v>0.256611257142857</v>
+        <v>0.257438571428571</v>
       </c>
       <c r="L181" s="34">
         <f t="shared" si="8"/>
@@ -11884,13 +11884,13 @@
         <v>6</v>
       </c>
       <c r="C182" s="28">
-        <v>2.582</v>
+        <v>2.59</v>
       </c>
       <c r="D182" s="67">
-        <v>0.38732</v>
+        <v>0.38609</v>
       </c>
       <c r="E182" s="28">
-        <v>4.88</v>
+        <v>4.61</v>
       </c>
       <c r="F182" s="28">
         <v>0</v>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="K182" s="32">
         <f t="shared" si="7"/>
-        <v>125.226293485714</v>
+        <v>118.679181428571</v>
       </c>
       <c r="L182" s="34">
         <f t="shared" si="8"/>
@@ -11928,10 +11928,10 @@
         <v>3.187</v>
       </c>
       <c r="D183" s="67">
-        <v>0.31373</v>
+        <v>0.3138</v>
       </c>
       <c r="E183" s="28">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="F183" s="28">
         <v>0</v>
@@ -11952,11 +11952,11 @@
       </c>
       <c r="K183" s="32">
         <f t="shared" si="7"/>
-        <v>100.848224057143</v>
+        <v>99.6287271428571</v>
       </c>
       <c r="L183" s="34">
         <f t="shared" si="8"/>
-        <v>0.256611257142857</v>
+        <v>0.257438571428571</v>
       </c>
       <c r="N183" s="10"/>
       <c r="O183" s="26"/>
@@ -11966,10 +11966,10 @@
         <v>8</v>
       </c>
       <c r="C184" s="28">
-        <v>3.282</v>
+        <v>3.277</v>
       </c>
       <c r="D184" s="67">
-        <v>0.30472</v>
+        <v>0.30515</v>
       </c>
       <c r="E184" s="28">
         <v>0</v>
@@ -11978,14 +11978,14 @@
         <v>0</v>
       </c>
       <c r="G184" s="28">
-        <v>79.04</v>
+        <v>79.18</v>
       </c>
       <c r="H184" s="28" t="s">
         <v>10</v>
       </c>
       <c r="I184" s="29">
         <f t="shared" si="5"/>
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="J184" s="31">
         <f t="shared" si="6"/>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="L184" s="34">
         <f t="shared" si="8"/>
-        <v>2028.25537645714</v>
+        <v>2038.39860857143</v>
       </c>
       <c r="N184" s="10"/>
       <c r="O184" s="26"/>
@@ -12361,7 +12361,7 @@
       </c>
       <c r="L191" s="34">
         <f t="shared" si="8"/>
-        <v>12.8305628571429</v>
+        <v>12.8719285714286</v>
       </c>
       <c r="N191" s="10"/>
       <c r="T191">
@@ -12394,10 +12394,10 @@
         <v>16</v>
       </c>
       <c r="C192" s="28">
-        <v>5.071</v>
+        <v>5.067</v>
       </c>
       <c r="D192" s="67">
-        <v>0.19719</v>
+        <v>0.19736</v>
       </c>
       <c r="E192" s="28">
         <v>0</v>
@@ -12406,7 +12406,7 @@
         <v>0</v>
       </c>
       <c r="G192" s="28">
-        <v>9.81</v>
+        <v>9.69</v>
       </c>
       <c r="H192" s="28" t="s">
         <v>10</v>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="L192" s="34">
         <f t="shared" si="8"/>
-        <v>251.735643257143</v>
+        <v>249.457975714286</v>
       </c>
       <c r="N192" s="10"/>
       <c r="T192">
@@ -12521,10 +12521,10 @@
         <v>18</v>
       </c>
       <c r="C194" s="28">
-        <v>5.439</v>
+        <v>5.44</v>
       </c>
       <c r="D194" s="67">
-        <v>0.18385</v>
+        <v>0.18383</v>
       </c>
       <c r="E194" s="28">
         <v>0.02</v>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="K194" s="32">
         <f t="shared" si="7"/>
-        <v>0.47900768</v>
+        <v>0.480552</v>
       </c>
       <c r="L194" s="34">
         <f t="shared" si="8"/>
@@ -12584,13 +12584,13 @@
         <v>19</v>
       </c>
       <c r="C195" s="28">
-        <v>7.178</v>
+        <v>7.196</v>
       </c>
       <c r="D195" s="67">
-        <v>0.13932</v>
+        <v>0.13897</v>
       </c>
       <c r="E195" s="28">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="F195" s="28">
         <v>0</v>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="K195" s="32">
         <f t="shared" si="7"/>
-        <v>17.24427648</v>
+        <v>17.9177245714286</v>
       </c>
       <c r="L195" s="34">
         <f t="shared" si="8"/>
@@ -12710,19 +12710,19 @@
         <v>21</v>
       </c>
       <c r="C197" s="28">
-        <v>7.321</v>
+        <v>7.333</v>
       </c>
       <c r="D197" s="67">
-        <v>0.1366</v>
+        <v>0.13638</v>
       </c>
       <c r="E197" s="28">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F197" s="28">
         <v>0</v>
       </c>
       <c r="G197" s="28">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H197" s="28" t="s">
         <v>10</v>
@@ -12737,11 +12737,11 @@
       </c>
       <c r="K197" s="32">
         <f t="shared" si="7"/>
-        <v>0.615867017142857</v>
+        <v>0</v>
       </c>
       <c r="L197" s="34">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.411901714285714</v>
       </c>
       <c r="T197">
         <v>8</v>
@@ -12773,38 +12773,38 @@
         <v>22</v>
       </c>
       <c r="C198" s="28">
-        <v>7.333</v>
+        <v>7.411</v>
       </c>
       <c r="D198" s="67">
-        <v>0.13637</v>
+        <v>0.13494</v>
       </c>
       <c r="E198" s="28">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="F198" s="28">
         <v>0</v>
       </c>
       <c r="G198" s="28">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H198" s="28" t="s">
         <v>10</v>
       </c>
       <c r="I198" s="29">
         <f t="shared" si="5"/>
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="J198" s="31">
         <f t="shared" si="6"/>
-        <v>0.137142857142857</v>
+        <v>0.131428571428571</v>
       </c>
       <c r="K198" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13.4211308571429</v>
       </c>
       <c r="L198" s="34">
         <f t="shared" si="8"/>
-        <v>0.410578011428572</v>
+        <v>0</v>
       </c>
       <c r="T198">
         <v>10</v>
@@ -12836,13 +12836,13 @@
         <v>23</v>
       </c>
       <c r="C199" s="28">
-        <v>7.432</v>
+        <v>7.498</v>
       </c>
       <c r="D199" s="67">
-        <v>0.13455</v>
+        <v>0.13337</v>
       </c>
       <c r="E199" s="28">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="F199" s="28">
         <v>0</v>
@@ -12863,7 +12863,7 @@
       </c>
       <c r="K199" s="32">
         <f t="shared" si="7"/>
-        <v>14.5584119885714</v>
+        <v>0</v>
       </c>
       <c r="L199" s="34">
         <f t="shared" si="8"/>
@@ -12899,13 +12899,13 @@
         <v>24</v>
       </c>
       <c r="C200" s="28">
-        <v>7.498</v>
+        <v>7.512</v>
       </c>
       <c r="D200" s="67">
-        <v>0.13337</v>
+        <v>0.13312</v>
       </c>
       <c r="E200" s="28">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F200" s="28">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="K200" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.89478285714286</v>
       </c>
       <c r="L200" s="34">
         <f t="shared" si="8"/>
@@ -12962,13 +12962,13 @@
         <v>25</v>
       </c>
       <c r="C201" s="28">
-        <v>7.516</v>
+        <v>7.523</v>
       </c>
       <c r="D201" s="67">
-        <v>0.13306</v>
+        <v>0.13293</v>
       </c>
       <c r="E201" s="28">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="F201" s="28">
         <v>0</v>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="K201" s="32">
         <f t="shared" si="7"/>
-        <v>6.49226480571429</v>
+        <v>0</v>
       </c>
       <c r="L201" s="34">
         <f t="shared" si="8"/>
@@ -13025,13 +13025,13 @@
         <v>26</v>
       </c>
       <c r="C202" s="28">
-        <v>7.523</v>
+        <v>7.527</v>
       </c>
       <c r="D202" s="67">
-        <v>0.13293</v>
+        <v>0.13285</v>
       </c>
       <c r="E202" s="28">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="F202" s="28">
         <v>0</v>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="K202" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.381587</v>
       </c>
       <c r="L202" s="34">
         <f t="shared" si="8"/>
@@ -13088,13 +13088,13 @@
         <v>27</v>
       </c>
       <c r="C203" s="28">
-        <v>7.529</v>
+        <v>7.53</v>
       </c>
       <c r="D203" s="67">
-        <v>0.13283</v>
+        <v>0.1328</v>
       </c>
       <c r="E203" s="28">
-        <v>0.07</v>
+        <v>0</v>
       </c>
       <c r="F203" s="28">
         <v>0</v>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="K203" s="32">
         <f t="shared" si="7"/>
-        <v>1.37714708</v>
+        <v>0</v>
       </c>
       <c r="L203" s="34">
         <f t="shared" si="8"/>
@@ -13151,13 +13151,13 @@
         <v>28</v>
       </c>
       <c r="C204" s="28">
-        <v>7.53</v>
+        <v>7.533</v>
       </c>
       <c r="D204" s="67">
-        <v>0.1328</v>
+        <v>0.13275</v>
       </c>
       <c r="E204" s="28">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F204" s="28">
         <v>0</v>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="K204" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.789478285714286</v>
       </c>
       <c r="L204" s="34">
         <f t="shared" si="8"/>
@@ -13215,13 +13215,13 @@
         <v>29</v>
       </c>
       <c r="C205" s="28">
-        <v>7.534</v>
+        <v>7.535</v>
       </c>
       <c r="D205" s="67">
-        <v>0.13273</v>
+        <v>0.13272</v>
       </c>
       <c r="E205" s="28">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F205" s="28">
         <v>0</v>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="K205" s="32">
         <f t="shared" si="7"/>
-        <v>0.590205891428571</v>
+        <v>0</v>
       </c>
       <c r="L205" s="34">
         <f t="shared" si="8"/>
@@ -13278,10 +13278,10 @@
         <v>30</v>
       </c>
       <c r="C206" s="28">
-        <v>7.535</v>
+        <v>7.537</v>
       </c>
       <c r="D206" s="67">
-        <v>0.13272</v>
+        <v>0.13269</v>
       </c>
       <c r="E206" s="28">
         <v>0</v>
@@ -13404,13 +13404,13 @@
         <v>32</v>
       </c>
       <c r="C208" s="28">
-        <v>7.537</v>
+        <v>7.538</v>
       </c>
       <c r="D208" s="67">
-        <v>0.13267</v>
+        <v>0.13265</v>
       </c>
       <c r="E208" s="28">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F208" s="28">
         <v>0</v>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="K208" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.197369571428571</v>
       </c>
       <c r="L208" s="34">
         <f t="shared" si="8"/>
@@ -13470,16 +13470,16 @@
         <v>7.551</v>
       </c>
       <c r="D209" s="67">
-        <v>0.13244</v>
+        <v>0.13243</v>
       </c>
       <c r="E209" s="28">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F209" s="28">
         <v>0</v>
       </c>
       <c r="G209" s="28">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="H209" s="28" t="s">
         <v>10</v>
@@ -13494,11 +13494,11 @@
       </c>
       <c r="K209" s="32">
         <f t="shared" si="7"/>
-        <v>0.196735297142857</v>
+        <v>0</v>
       </c>
       <c r="L209" s="34">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.57895657142857</v>
       </c>
       <c r="T209">
         <v>24</v>
@@ -13530,19 +13530,19 @@
         <v>34</v>
       </c>
       <c r="C210" s="28">
-        <v>7.551</v>
+        <v>7.608</v>
       </c>
       <c r="D210" s="67">
-        <v>0.13243</v>
+        <v>0.13144</v>
       </c>
       <c r="E210" s="28">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="F210" s="28">
         <v>0</v>
       </c>
       <c r="G210" s="28">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H210" s="28" t="s">
         <v>10</v>
@@ -13557,11 +13557,11 @@
       </c>
       <c r="K210" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.72371757142857</v>
       </c>
       <c r="L210" s="34">
         <f t="shared" si="8"/>
-        <v>1.57388237714286</v>
+        <v>0</v>
       </c>
       <c r="T210">
         <v>25</v>
@@ -13599,7 +13599,7 @@
         <v>0.13144</v>
       </c>
       <c r="E211" s="28">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="F211" s="28">
         <v>0</v>
@@ -13620,7 +13620,7 @@
       </c>
       <c r="K211" s="32">
         <f t="shared" si="7"/>
-        <v>5.70532361714286</v>
+        <v>5.32897842857143</v>
       </c>
       <c r="L211" s="34">
         <f t="shared" si="8"/>
@@ -13656,13 +13656,13 @@
         <v>36</v>
       </c>
       <c r="C212" s="28">
-        <v>7.608</v>
+        <v>7.69</v>
       </c>
       <c r="D212" s="67">
-        <v>0.13144</v>
+        <v>0.13004</v>
       </c>
       <c r="E212" s="28">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="F212" s="28">
         <v>0</v>
@@ -13683,7 +13683,7 @@
       </c>
       <c r="K212" s="32">
         <f t="shared" si="7"/>
-        <v>5.31185302285714</v>
+        <v>0</v>
       </c>
       <c r="L212" s="34">
         <f t="shared" si="8"/>
@@ -13719,13 +13719,13 @@
         <v>37</v>
       </c>
       <c r="C213" s="28">
-        <v>8.331</v>
+        <v>8.411</v>
       </c>
       <c r="D213" s="67">
-        <v>0.12004</v>
+        <v>0.11889</v>
       </c>
       <c r="E213" s="28">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="F213" s="28">
         <v>0</v>
@@ -13746,7 +13746,7 @@
       </c>
       <c r="K213" s="32">
         <f t="shared" si="7"/>
-        <v>15.0545270857143</v>
+        <v>13.7815448571429</v>
       </c>
       <c r="L213" s="34">
         <f t="shared" si="8"/>
@@ -13782,10 +13782,10 @@
         <v>38</v>
       </c>
       <c r="C214" s="28">
-        <v>8.801</v>
+        <v>8.802</v>
       </c>
       <c r="D214" s="67">
-        <v>0.11362</v>
+        <v>0.11361</v>
       </c>
       <c r="E214" s="28">
         <v>0</v>
@@ -13845,19 +13845,19 @@
         <v>39</v>
       </c>
       <c r="C215" s="28">
-        <v>9.31</v>
+        <v>9.324</v>
       </c>
       <c r="D215" s="67">
-        <v>0.10741</v>
+        <v>0.10726</v>
       </c>
       <c r="E215" s="28">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F215" s="28">
         <v>0</v>
       </c>
       <c r="G215" s="28">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="H215" s="28" t="s">
         <v>10</v>
@@ -13872,11 +13872,11 @@
       </c>
       <c r="K215" s="32">
         <f t="shared" si="7"/>
-        <v>3.5925576</v>
+        <v>1.80207</v>
       </c>
       <c r="L215" s="34">
         <f t="shared" si="8"/>
-        <v>28.38120504</v>
+        <v>41.988231</v>
       </c>
       <c r="T215">
         <v>30</v>
@@ -13908,19 +13908,19 @@
         <v>40</v>
       </c>
       <c r="C216" s="28">
-        <v>9.389</v>
+        <v>9.418</v>
       </c>
       <c r="D216" s="67">
-        <v>0.10651</v>
+        <v>0.10617</v>
       </c>
       <c r="E216" s="28">
-        <v>0.35</v>
+        <v>0.49</v>
       </c>
       <c r="F216" s="28">
         <v>0</v>
       </c>
       <c r="G216" s="28">
-        <v>1.35</v>
+        <v>0.67</v>
       </c>
       <c r="H216" s="28" t="s">
         <v>10</v>
@@ -13935,11 +13935,11 @@
       </c>
       <c r="K216" s="32">
         <f t="shared" si="7"/>
-        <v>6.2869758</v>
+        <v>8.830143</v>
       </c>
       <c r="L216" s="34">
         <f t="shared" si="8"/>
-        <v>24.2497638</v>
+        <v>12.073869</v>
       </c>
       <c r="T216">
         <v>31</v>
@@ -13971,38 +13971,38 @@
         <v>41</v>
       </c>
       <c r="C217" s="28">
-        <v>9.52</v>
+        <v>9.63</v>
       </c>
       <c r="D217" s="67">
-        <v>0.10504</v>
+        <v>0.10384</v>
       </c>
       <c r="E217" s="28">
-        <v>0.21</v>
+        <v>0.5</v>
       </c>
       <c r="F217" s="28">
         <v>0</v>
       </c>
       <c r="G217" s="28">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="H217" s="28" t="s">
         <v>10</v>
       </c>
       <c r="I217" s="29">
         <f t="shared" si="5"/>
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J217" s="31">
         <f t="shared" si="6"/>
-        <v>0.12</v>
+        <v>0.114285714285714</v>
       </c>
       <c r="K217" s="32">
         <f t="shared" si="7"/>
-        <v>3.77218548</v>
+        <v>8.58128571428571</v>
       </c>
       <c r="L217" s="34">
         <f t="shared" si="8"/>
-        <v>1.61665092</v>
+        <v>0.343251428571429</v>
       </c>
       <c r="T217">
         <v>32</v>
@@ -14034,13 +14034,13 @@
         <v>42</v>
       </c>
       <c r="C218" s="28">
-        <v>10.015</v>
+        <v>10.434</v>
       </c>
       <c r="D218" s="67">
-        <v>0.09985</v>
+        <v>0.09584</v>
       </c>
       <c r="E218" s="28">
-        <v>0.17</v>
+        <v>0.04</v>
       </c>
       <c r="F218" s="28">
         <v>0</v>
@@ -14061,7 +14061,7 @@
       </c>
       <c r="K218" s="32">
         <f t="shared" si="7"/>
-        <v>2.90826091428572</v>
+        <v>0.686502857142857</v>
       </c>
       <c r="L218" s="34">
         <f t="shared" si="8"/>
@@ -14160,13 +14160,13 @@
         <v>44</v>
       </c>
       <c r="C220" s="28">
-        <v>10.837</v>
+        <v>10.854</v>
       </c>
       <c r="D220" s="67">
-        <v>0.09228</v>
+        <v>0.09214</v>
       </c>
       <c r="E220" s="28">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="F220" s="28">
         <v>0</v>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="K220" s="32">
         <f t="shared" si="7"/>
-        <v>0.812602314285714</v>
+        <v>0.978266571428571</v>
       </c>
       <c r="L220" s="34">
         <f t="shared" si="8"/>
@@ -14218,43 +14218,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="2:27" ht="15.6" customHeight="1">
-      <c r="B221" s="33">
-        <v>45</v>
-      </c>
-      <c r="C221" s="28">
-        <v>10.859</v>
-      </c>
-      <c r="D221" s="67">
-        <v>0.09209</v>
-      </c>
-      <c r="E221" s="28">
-        <v>0.01</v>
-      </c>
-      <c r="F221" s="28">
-        <v>0</v>
-      </c>
-      <c r="G221" s="28">
-        <v>0</v>
-      </c>
-      <c r="H221" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="I221" s="29">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
-      </c>
-      <c r="J221" s="31">
-        <f t="shared" si="6"/>
-        <v>0.108571428571429</v>
-      </c>
-      <c r="K221" s="32">
-        <f t="shared" si="7"/>
-        <v>0.162520462857143</v>
-      </c>
-      <c r="L221" s="34">
-        <f t="shared" si="8"/>
-        <v>0</v>
+    <row r="221" spans="2:27" ht="19.5" customHeight="1" thickBot="1">
+      <c r="B221" s="121" t="s">
+        <v>24</v>
+      </c>
+      <c r="C221" s="122"/>
+      <c r="D221" s="122"/>
+      <c r="E221" s="123">
+        <f>SUM(E177:E220)</f>
+        <v>90.13</v>
+      </c>
+      <c r="F221" s="123">
+        <f t="shared" ref="F221" si="9">SUM(F177:F220)</f>
+        <v>0</v>
+      </c>
+      <c r="G221" s="123">
+        <f>SUM(G177:G220)</f>
+        <v>92.5</v>
+      </c>
+      <c r="H221" s="141" t="s">
+        <v>84</v>
+      </c>
+      <c r="I221" s="142"/>
+      <c r="J221" s="143"/>
+      <c r="K221" s="124">
+        <f>SQRT(SUMSQ(K177:K220))</f>
+        <v>1780.02971972459</v>
+      </c>
+      <c r="L221" s="124">
+        <f>SQRT(SUMSQ(L177:L220))</f>
+        <v>2054.1118500064</v>
       </c>
       <c r="T221">
         <v>53</v>
@@ -14281,44 +14274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="2:27" ht="15.6" customHeight="1">
-      <c r="B222" s="33">
-        <v>46</v>
-      </c>
-      <c r="C222" s="28">
-        <v>10.862</v>
-      </c>
-      <c r="D222" s="67">
-        <v>0.09206</v>
-      </c>
-      <c r="E222" s="28">
-        <v>0</v>
-      </c>
-      <c r="F222" s="28">
-        <v>0</v>
-      </c>
-      <c r="G222" s="28">
-        <v>0</v>
-      </c>
-      <c r="H222" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="I222" s="29">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
-      </c>
-      <c r="J222" s="31">
-        <f t="shared" si="6"/>
-        <v>0.108571428571429</v>
-      </c>
-      <c r="K222" s="32">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L222" s="34">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+    <row r="222" spans="2:27">
       <c r="T222">
         <v>54</v>
       </c>
@@ -14344,43 +14300,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="2:27" ht="15.6" customHeight="1">
-      <c r="B223" s="33">
-        <v>47</v>
-      </c>
-      <c r="C223" s="28">
-        <v>10.877</v>
-      </c>
-      <c r="D223" s="67">
-        <v>0.09194</v>
-      </c>
-      <c r="E223" s="28">
-        <v>0</v>
-      </c>
-      <c r="F223" s="28">
-        <v>0</v>
-      </c>
-      <c r="G223" s="28">
-        <v>0</v>
-      </c>
-      <c r="H223" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="I223" s="29">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
-      </c>
-      <c r="J223" s="31">
-        <f t="shared" si="6"/>
-        <v>0.108571428571429</v>
-      </c>
-      <c r="K223" s="32">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L223" s="34">
-        <f t="shared" si="8"/>
-        <v>0</v>
+    <row r="223" spans="2:27" ht="15.6">
+      <c r="H223" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="J223" s="44" t="s">
+        <v>242</v>
+      </c>
+      <c r="K223" s="30">
+        <f>E165</f>
+        <v>15017.25</v>
+      </c>
+      <c r="L223" t="s">
+        <v>9</v>
       </c>
       <c r="T223">
         <v>55</v>
@@ -14407,43 +14339,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="2:27" ht="15.6" customHeight="1">
-      <c r="B224" s="33">
-        <v>48</v>
-      </c>
-      <c r="C224" s="28">
-        <v>10.879</v>
-      </c>
-      <c r="D224" s="67">
-        <v>0.09192</v>
-      </c>
-      <c r="E224" s="28">
-        <v>0.02</v>
-      </c>
-      <c r="F224" s="28">
-        <v>0</v>
-      </c>
-      <c r="G224" s="28">
-        <v>0</v>
-      </c>
-      <c r="H224" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="I224" s="29">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
-      </c>
-      <c r="J224" s="31">
-        <f t="shared" si="6"/>
-        <v>0.108571428571429</v>
-      </c>
-      <c r="K224" s="32">
-        <f t="shared" si="7"/>
-        <v>0.325040925714286</v>
-      </c>
-      <c r="L224" s="34">
-        <f t="shared" si="8"/>
-        <v>0</v>
+    <row r="224" spans="2:27" ht="15.6">
+      <c r="H224" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="J224" s="44" t="s">
+        <v>244</v>
+      </c>
+      <c r="K224" s="30">
+        <f>E166</f>
+        <v>15017.25</v>
+      </c>
+      <c r="L224" t="s">
+        <v>9</v>
       </c>
       <c r="T224">
         <v>56</v>
@@ -14470,44 +14378,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="2:27" ht="15.6" customHeight="1">
-      <c r="B225" s="33">
-        <v>49</v>
-      </c>
-      <c r="C225" s="28">
-        <v>10.887</v>
-      </c>
-      <c r="D225" s="67">
-        <v>0.09185</v>
-      </c>
-      <c r="E225" s="28">
-        <v>0</v>
-      </c>
-      <c r="F225" s="28">
-        <v>0</v>
-      </c>
-      <c r="G225" s="28">
-        <v>0</v>
-      </c>
-      <c r="H225" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="I225" s="29">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
-      </c>
-      <c r="J225" s="31">
-        <f t="shared" si="6"/>
-        <v>0.108571428571429</v>
-      </c>
-      <c r="K225" s="32">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L225" s="34">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+    <row r="225" spans="2:27">
+      <c r="K225" s="55"/>
+      <c r="L225" s="55"/>
       <c r="T225">
         <v>57</v>
       </c>
@@ -14533,43 +14406,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="2:27" ht="15.6" customHeight="1">
-      <c r="B226" s="33">
-        <v>50</v>
-      </c>
-      <c r="C226" s="28">
-        <v>10.888</v>
-      </c>
-      <c r="D226" s="67">
-        <v>0.09185</v>
-      </c>
-      <c r="E226" s="28">
-        <v>0</v>
-      </c>
-      <c r="F226" s="28">
-        <v>0</v>
-      </c>
-      <c r="G226" s="28">
-        <v>0</v>
-      </c>
-      <c r="H226" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="I226" s="29">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
-      </c>
-      <c r="J226" s="31">
-        <f t="shared" si="6"/>
-        <v>0.108571428571429</v>
-      </c>
-      <c r="K226" s="32">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L226" s="34">
-        <f t="shared" si="8"/>
-        <v>0</v>
+    <row r="226" spans="2:27">
+      <c r="H226" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="J226" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="K226" s="30">
+        <f>K223*VLOOKUP(MAX(E177:E220),E177:J220,6,0)</f>
+        <v>2301.10031159237</v>
+      </c>
+      <c r="L226" s="30">
+        <f>K223*VLOOKUP(MAX(G177:G220),G177:J220,4,0)</f>
+        <v>2574.38571428571</v>
       </c>
       <c r="T226">
         <v>58</v>
@@ -14596,43 +14446,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="2:27" ht="15.6" customHeight="1">
-      <c r="B227" s="33">
-        <v>51</v>
-      </c>
-      <c r="C227" s="28">
-        <v>10.894</v>
-      </c>
-      <c r="D227" s="67">
-        <v>0.0918</v>
-      </c>
-      <c r="E227" s="28">
-        <v>0</v>
-      </c>
-      <c r="F227" s="28">
-        <v>0</v>
-      </c>
-      <c r="G227" s="28">
-        <v>0</v>
-      </c>
-      <c r="H227" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="I227" s="29">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
-      </c>
-      <c r="J227" s="31">
-        <f t="shared" si="6"/>
-        <v>0.108571428571429</v>
-      </c>
-      <c r="K227" s="32">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L227" s="34">
-        <f t="shared" si="8"/>
-        <v>0</v>
+    <row r="227" spans="2:27">
+      <c r="J227" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="K227" s="30">
+        <f>0.9*K226</f>
+        <v>2070.99028043313</v>
+      </c>
+      <c r="L227" s="30">
+        <f>0.9*L226</f>
+        <v>2316.94714285714</v>
       </c>
       <c r="T227">
         <v>59</v>
@@ -14659,44 +14483,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="2:27" ht="15.6" customHeight="1">
-      <c r="B228" s="33">
-        <v>52</v>
-      </c>
-      <c r="C228" s="28">
-        <v>10.894</v>
-      </c>
-      <c r="D228" s="67">
-        <v>0.09179</v>
-      </c>
-      <c r="E228" s="28">
-        <v>0</v>
-      </c>
-      <c r="F228" s="28">
-        <v>0</v>
-      </c>
-      <c r="G228" s="28">
-        <v>0</v>
-      </c>
-      <c r="H228" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="I228" s="29">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
-      </c>
-      <c r="J228" s="31">
-        <f t="shared" si="6"/>
-        <v>0.108571428571429</v>
-      </c>
-      <c r="K228" s="32">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L228" s="34">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+    <row r="228" spans="2:27">
+      <c r="J228" s="12"/>
+      <c r="K228" s="55"/>
+      <c r="L228" s="55"/>
       <c r="T228">
         <v>60</v>
       </c>
@@ -14722,43 +14512,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="2:27" ht="15.6" customHeight="1">
-      <c r="B229" s="33">
-        <v>53</v>
-      </c>
-      <c r="C229" s="28">
-        <v>10.988</v>
-      </c>
-      <c r="D229" s="67">
-        <v>0.09101</v>
-      </c>
-      <c r="E229" s="28">
-        <v>0.18</v>
-      </c>
-      <c r="F229" s="28">
-        <v>0</v>
-      </c>
-      <c r="G229" s="28">
-        <v>0</v>
-      </c>
-      <c r="H229" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="I229" s="29">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
-      </c>
-      <c r="J229" s="31">
-        <f t="shared" si="6"/>
-        <v>0.108571428571429</v>
-      </c>
-      <c r="K229" s="32">
-        <f t="shared" si="7"/>
-        <v>2.92536833142857</v>
-      </c>
-      <c r="L229" s="34">
-        <f t="shared" si="8"/>
-        <v>0</v>
+    <row r="229" spans="2:27">
+      <c r="H229" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="J229" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="K229" s="30">
+        <f>K223*G168</f>
+        <v>2574.38571428571</v>
+      </c>
+      <c r="L229" s="30">
+        <f>K223*G168</f>
+        <v>2574.38571428571</v>
       </c>
       <c r="T229">
         <v>61</v>
@@ -14785,43 +14552,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="2:27" ht="15.6" customHeight="1">
-      <c r="B230" s="33">
-        <v>54</v>
-      </c>
-      <c r="C230" s="28">
-        <v>11.087</v>
-      </c>
-      <c r="D230" s="67">
-        <v>0.09019</v>
-      </c>
-      <c r="E230" s="28">
-        <v>0</v>
-      </c>
-      <c r="F230" s="28">
-        <v>0</v>
-      </c>
-      <c r="G230" s="28">
-        <v>0</v>
-      </c>
-      <c r="H230" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="I230" s="29">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
-      </c>
-      <c r="J230" s="31">
-        <f t="shared" si="6"/>
-        <v>0.108571428571429</v>
-      </c>
-      <c r="K230" s="32">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L230" s="34">
-        <f t="shared" si="8"/>
-        <v>0</v>
+    <row r="230" spans="2:27">
+      <c r="J230" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="K230" s="30">
+        <f>0.8*K229</f>
+        <v>2059.50857142857</v>
+      </c>
+      <c r="L230" s="30">
+        <f>0.8*L229</f>
+        <v>2059.50857142857</v>
       </c>
       <c r="T230">
         <v>62</v>
@@ -14848,44 +14589,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="2:27" ht="15.6" customHeight="1">
-      <c r="B231" s="33">
-        <v>55</v>
-      </c>
-      <c r="C231" s="28">
-        <v>11.105</v>
-      </c>
-      <c r="D231" s="67">
-        <v>0.09005</v>
-      </c>
-      <c r="E231" s="28">
-        <v>0.24</v>
-      </c>
-      <c r="F231" s="28">
-        <v>0</v>
-      </c>
-      <c r="G231" s="28">
-        <v>0</v>
-      </c>
-      <c r="H231" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="I231" s="29">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
-      </c>
-      <c r="J231" s="31">
-        <f t="shared" si="6"/>
-        <v>0.108571428571429</v>
-      </c>
-      <c r="K231" s="32">
-        <f t="shared" si="7"/>
-        <v>3.90049110857143</v>
-      </c>
-      <c r="L231" s="34">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+    <row r="231" spans="2:27">
+      <c r="J231" s="12"/>
       <c r="T231">
         <v>63</v>
       </c>
@@ -14911,37 +14616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="2:27" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B232" s="121" t="s">
-        <v>24</v>
-      </c>
-      <c r="C232" s="122"/>
-      <c r="D232" s="122"/>
-      <c r="E232" s="123">
-        <f>SUM(E177:E231)</f>
-        <v>90.37</v>
-      </c>
-      <c r="F232" s="123">
-        <f t="shared" ref="F232" si="9">SUM(F177:F231)</f>
-        <v>0</v>
-      </c>
-      <c r="G232" s="123">
-        <f>SUM(G177:G231)</f>
-        <v>92.48</v>
-      </c>
-      <c r="H232" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="I232" s="142"/>
-      <c r="J232" s="143"/>
-      <c r="K232" s="124">
-        <f>SQRT(SUMSQ(K177:K231))</f>
-        <v>1766.18550138523</v>
-      </c>
-      <c r="L232" s="124">
-        <f>SQRT(SUMSQ(L177:L231))</f>
-        <v>2044.20013660358</v>
-      </c>
+    <row r="232" spans="2:27">
       <c r="T232">
         <v>64</v>
       </c>
@@ -14968,6 +14643,20 @@
       </c>
     </row>
     <row r="233" spans="2:27">
+      <c r="H233" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="J233" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="K233" s="45">
+        <f>MAX(K230,K227)</f>
+        <v>2070.99028043313</v>
+      </c>
+      <c r="L233" s="45">
+        <f>MAX(L230,L227)</f>
+        <v>2316.94714285714</v>
+      </c>
       <c r="T233">
         <v>65</v>
       </c>
@@ -14993,20 +14682,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="2:27" ht="15.6">
-      <c r="H234" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="J234" s="44" t="s">
-        <v>242</v>
-      </c>
-      <c r="K234" s="30">
-        <f>E165</f>
-        <v>14968.99</v>
-      </c>
-      <c r="L234" t="s">
-        <v>9</v>
-      </c>
+    <row r="234" spans="2:27">
+      <c r="H234" s="12"/>
       <c r="T234">
         <v>66</v>
       </c>
@@ -15032,20 +14709,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="2:27" ht="15.6">
-      <c r="H235" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="J235" s="44" t="s">
-        <v>244</v>
-      </c>
-      <c r="K235" s="30">
-        <f>E166</f>
-        <v>14968.99</v>
-      </c>
-      <c r="L235" t="s">
-        <v>9</v>
-      </c>
+    <row r="235" spans="2:27">
+      <c r="K235" s="135" t="s">
+        <v>199</v>
+      </c>
+      <c r="L235" s="136"/>
       <c r="T235">
         <v>67</v>
       </c>
@@ -15072,8 +14740,12 @@
       </c>
     </row>
     <row r="236" spans="2:27">
-      <c r="K236" s="55"/>
-      <c r="L236" s="55"/>
+      <c r="K236" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="L236" s="23" t="s">
+        <v>38</v>
+      </c>
       <c r="T236">
         <v>68</v>
       </c>
@@ -15100,19 +14772,16 @@
       </c>
     </row>
     <row r="237" spans="2:27">
-      <c r="H237" s="12" t="s">
-        <v>191</v>
-      </c>
       <c r="J237" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="K237" s="30">
-        <f>K234*VLOOKUP(MAX(E177:E231),E177:J231,6,0)</f>
-        <v>2293.70540899453</v>
-      </c>
-      <c r="L237" s="30">
-        <f>K234*VLOOKUP(MAX(G177:G231),G177:J231,4,0)</f>
-        <v>2566.11257142857</v>
+        <v>230</v>
+      </c>
+      <c r="K237" s="48">
+        <f>K233/1000</f>
+        <v>2.07099028043313</v>
+      </c>
+      <c r="L237" s="48">
+        <f>L233/1000</f>
+        <v>2.31694714285714</v>
       </c>
       <c r="T237">
         <v>69</v>
@@ -15141,15 +14810,15 @@
     </row>
     <row r="238" spans="2:27">
       <c r="J238" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="K238" s="30">
-        <f>0.9*K237</f>
-        <v>2064.33486809507</v>
-      </c>
-      <c r="L238" s="30">
-        <f>0.9*L237</f>
-        <v>2309.50131428571</v>
+        <v>228</v>
+      </c>
+      <c r="K238" s="48">
+        <f>K221/1000</f>
+        <v>1.78002971972459</v>
+      </c>
+      <c r="L238" s="48">
+        <f>L221/1000</f>
+        <v>2.0541118500064</v>
       </c>
       <c r="T238">
         <v>70</v>
@@ -15177,9 +14846,17 @@
       </c>
     </row>
     <row r="239" spans="2:27">
-      <c r="J239" s="12"/>
-      <c r="K239" s="55"/>
-      <c r="L239" s="55"/>
+      <c r="J239" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="K239" s="71" t="str">
+        <f>IF(K221&gt;=K233,"Se Cumple","No se Cumple")</f>
+        <v>No se Cumple</v>
+      </c>
+      <c r="L239" s="71" t="str">
+        <f>IF(L221&gt;=K233,"Se Cumple","No se Cumple")</f>
+        <v>No se Cumple</v>
+      </c>
       <c r="T239">
         <v>71</v>
       </c>
@@ -15206,19 +14883,16 @@
       </c>
     </row>
     <row r="240" spans="2:27">
-      <c r="H240" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="J240" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="K240" s="30">
-        <f>K234*G168</f>
-        <v>2566.11257142857</v>
-      </c>
-      <c r="L240" s="30">
-        <f>K234*G168</f>
-        <v>2566.11257142857</v>
+      <c r="J240" s="61" t="s">
+        <v>231</v>
+      </c>
+      <c r="K240" s="92">
+        <f>MAX(K237/K238,1)</f>
+        <v>1.16345825998544</v>
+      </c>
+      <c r="L240" s="92">
+        <f>MAX(L237/L238,1)</f>
+        <v>1.12795568695537</v>
       </c>
       <c r="T240">
         <v>72</v>
@@ -15246,17 +14920,6 @@
       </c>
     </row>
     <row r="241" spans="2:27">
-      <c r="J241" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="K241" s="30">
-        <f>0.8*K240</f>
-        <v>2052.89005714286</v>
-      </c>
-      <c r="L241" s="30">
-        <f>0.8*L240</f>
-        <v>2052.89005714286</v>
-      </c>
       <c r="T241">
         <v>73</v>
       </c>
@@ -15283,7 +14946,17 @@
       </c>
     </row>
     <row r="242" spans="2:27">
-      <c r="J242" s="12"/>
+      <c r="J242" s="61" t="s">
+        <v>198</v>
+      </c>
+      <c r="K242" s="92">
+        <f>IF(K227/K221&lt;1,"N/A",K227/K221)</f>
+        <v>1.16345825998544</v>
+      </c>
+      <c r="L242" s="92">
+        <f>IF(L227/L221&lt;1,"N/A",L227/L221)</f>
+        <v>1.12795568695537</v>
+      </c>
       <c r="T242">
         <v>74</v>
       </c>
@@ -15336,19 +15009,13 @@
       </c>
     </row>
     <row r="244" spans="2:27">
-      <c r="H244" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="J244" s="44" t="s">
-        <v>196</v>
-      </c>
-      <c r="K244" s="45">
-        <f>MAX(K241,K238)</f>
-        <v>2064.33486809507</v>
-      </c>
-      <c r="L244" s="45">
-        <f>MAX(L241,L238)</f>
-        <v>2309.50131428571</v>
+      <c r="K244" s="55">
+        <f>K226/K221</f>
+        <v>1.29273139998382</v>
+      </c>
+      <c r="L244" s="55">
+        <f>L226/L221</f>
+        <v>1.25328409661708</v>
       </c>
       <c r="T244">
         <v>76</v>
@@ -15376,7 +15043,6 @@
       </c>
     </row>
     <row r="245" spans="2:27">
-      <c r="H245" s="12"/>
       <c r="T245">
         <v>77</v>
       </c>
@@ -15403,10 +15069,6 @@
       </c>
     </row>
     <row r="246" spans="2:27">
-      <c r="K246" s="135" t="s">
-        <v>199</v>
-      </c>
-      <c r="L246" s="136"/>
       <c r="T246">
         <v>78</v>
       </c>
@@ -15432,13 +15094,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="2:27">
-      <c r="K247" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="L247" s="23" t="s">
-        <v>38</v>
-      </c>
+    <row r="247" spans="2:27" ht="15" thickBot="1">
+      <c r="B247" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C247" s="4"/>
+      <c r="D247" s="4"/>
+      <c r="E247" s="4"/>
+      <c r="F247" s="4"/>
+      <c r="G247" s="4"/>
+      <c r="H247" s="4"/>
+      <c r="I247" s="4"/>
+      <c r="J247" s="4"/>
+      <c r="K247" s="4"/>
+      <c r="L247" s="4"/>
+      <c r="M247" s="4"/>
+      <c r="N247" s="4"/>
+      <c r="O247" s="4"/>
       <c r="T247">
         <v>79</v>
       </c>
@@ -15465,17 +15137,6 @@
       </c>
     </row>
     <row r="248" spans="2:27">
-      <c r="J248" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="K248" s="48">
-        <f>K244/1000</f>
-        <v>2.06433486809507</v>
-      </c>
-      <c r="L248" s="48">
-        <f>L244/1000</f>
-        <v>2.30950131428572</v>
-      </c>
       <c r="T248">
         <v>80</v>
       </c>
@@ -15502,16 +15163,8 @@
       </c>
     </row>
     <row r="249" spans="2:27">
-      <c r="J249" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="K249" s="48">
-        <f>K232/1000</f>
-        <v>1.76618550138523</v>
-      </c>
-      <c r="L249" s="48">
-        <f>L232/1000</f>
-        <v>2.04420013660358</v>
+      <c r="B249" t="s">
+        <v>68</v>
       </c>
       <c r="T249">
         <v>81</v>
@@ -15539,17 +15192,6 @@
       </c>
     </row>
     <row r="250" spans="2:27">
-      <c r="J250" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="K250" s="71" t="str">
-        <f>IF(K232&gt;=K244,"Se Cumple","No se Cumple")</f>
-        <v>No se Cumple</v>
-      </c>
-      <c r="L250" s="71" t="str">
-        <f>IF(L232&gt;=K244,"Se Cumple","No se Cumple")</f>
-        <v>No se Cumple</v>
-      </c>
       <c r="T250">
         <v>82</v>
       </c>
@@ -15576,16 +15218,18 @@
       </c>
     </row>
     <row r="251" spans="2:27">
-      <c r="J251" s="61" t="s">
-        <v>231</v>
-      </c>
-      <c r="K251" s="92">
-        <f>MAX(K248/K249,1)</f>
-        <v>1.16880976911882</v>
-      </c>
-      <c r="L251" s="92">
-        <f>MAX(L248/L249,1)</f>
-        <v>1.12978238917591</v>
+      <c r="B251" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C251" s="40">
+        <f>P33</f>
+        <v>0.4</v>
+      </c>
+      <c r="H251" t="s">
+        <v>71</v>
+      </c>
+      <c r="I251" t="s">
+        <v>72</v>
       </c>
       <c r="T251">
         <v>83</v>
@@ -15613,6 +15257,19 @@
       </c>
     </row>
     <row r="252" spans="2:27">
+      <c r="B252" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C252" s="40">
+        <f>P55</f>
+        <v>3</v>
+      </c>
+      <c r="H252" t="s">
+        <v>29</v>
+      </c>
+      <c r="I252" t="s">
+        <v>34</v>
+      </c>
       <c r="T252">
         <v>84</v>
       </c>
@@ -15639,16 +15296,18 @@
       </c>
     </row>
     <row r="253" spans="2:27">
-      <c r="J253" s="61" t="s">
-        <v>198</v>
-      </c>
-      <c r="K253" s="92">
-        <f>IF(K238/K232&lt;1,"N/A",K238/K232)</f>
-        <v>1.16880976911882</v>
-      </c>
-      <c r="L253" s="92">
-        <f>IF(L238/L232&lt;1,"N/A",L238/L232)</f>
-        <v>1.12978238917591</v>
+      <c r="B253" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C253" s="40">
+        <f>P57</f>
+        <v>0.6</v>
+      </c>
+      <c r="H253">
+        <v>0.01</v>
+      </c>
+      <c r="I253" s="55">
+        <v>6.2857142857142861E-2</v>
       </c>
       <c r="T253">
         <v>85</v>
@@ -15676,6 +15335,20 @@
       </c>
     </row>
     <row r="254" spans="2:27">
+      <c r="B254" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C254" s="40">
+        <f>Q85</f>
+        <v>1</v>
+      </c>
+      <c r="H254">
+        <v>0.02</v>
+      </c>
+      <c r="I254" s="55">
+        <f>IF(H254&lt;$C$253/3,   ($C$254*$C$251/$C$255)*(1+(3*($C$252-1)*H254/$C$253)),   IF(H254&lt;=$C$253,   $C$254*$C$251*$C$252/$C$255,   $C$254*$C$251*$C$252/$C$255*($C$253/H254)^(2/3)   ))</f>
+        <v>6.8571428571428575E-2</v>
+      </c>
       <c r="T254">
         <v>88</v>
       </c>
@@ -15702,13 +15375,19 @@
       </c>
     </row>
     <row r="255" spans="2:27">
-      <c r="K255" s="55">
-        <f>K237/K232</f>
-        <v>1.29867752124313</v>
-      </c>
-      <c r="L255" s="55">
-        <f>L237/L232</f>
-        <v>1.25531376575101</v>
+      <c r="B255" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C255" s="40">
+        <f>P99</f>
+        <v>7</v>
+      </c>
+      <c r="H255">
+        <v>0.03</v>
+      </c>
+      <c r="I255" s="55">
+        <f t="shared" ref="I254:I317" si="10">IF(H255&lt;$C$253/3,   ($C$254*$C$251/$C$255)*(1+(3*($C$252-1)*H255/$C$253)),   IF(H255&lt;=$C$253,   $C$254*$C$251*$C$252/$C$255,   $C$254*$C$251*$C$252/$C$255*($C$253/H255)^(2/3)   ))</f>
+        <v>7.4285714285714288E-2</v>
       </c>
       <c r="T255">
         <v>90</v>
@@ -15736,6 +15415,20 @@
       </c>
     </row>
     <row r="256" spans="2:27">
+      <c r="B256" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C256" s="40">
+        <f>P97</f>
+        <v>6</v>
+      </c>
+      <c r="H256">
+        <v>0.04</v>
+      </c>
+      <c r="I256" s="55">
+        <f t="shared" si="10"/>
+        <v>0.08</v>
+      </c>
       <c r="T256">
         <v>92</v>
       </c>
@@ -15762,6 +15455,13 @@
       </c>
     </row>
     <row r="257" spans="2:27">
+      <c r="H257">
+        <v>0.05</v>
+      </c>
+      <c r="I257" s="55">
+        <f t="shared" si="10"/>
+        <v>8.5714285714285715E-2</v>
+      </c>
       <c r="T257">
         <v>94</v>
       </c>
@@ -15787,23 +15487,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="2:27" ht="15" thickBot="1">
-      <c r="B258" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C258" s="4"/>
-      <c r="D258" s="4"/>
-      <c r="E258" s="4"/>
-      <c r="F258" s="4"/>
-      <c r="G258" s="4"/>
-      <c r="H258" s="4"/>
-      <c r="I258" s="4"/>
-      <c r="J258" s="4"/>
-      <c r="K258" s="4"/>
-      <c r="L258" s="4"/>
-      <c r="M258" s="4"/>
-      <c r="N258" s="4"/>
-      <c r="O258" s="4"/>
+    <row r="258" spans="2:27">
+      <c r="H258">
+        <v>0.06</v>
+      </c>
+      <c r="I258" s="55">
+        <f t="shared" si="10"/>
+        <v>9.1428571428571442E-2</v>
+      </c>
       <c r="T258">
         <v>97</v>
       </c>
@@ -15830,6 +15521,13 @@
       </c>
     </row>
     <row r="259" spans="2:27">
+      <c r="H259">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I259" s="55">
+        <f t="shared" si="10"/>
+        <v>9.7142857142857156E-2</v>
+      </c>
       <c r="T259">
         <v>101</v>
       </c>
@@ -15856,8 +15554,12 @@
       </c>
     </row>
     <row r="260" spans="2:27">
-      <c r="B260" t="s">
-        <v>68</v>
+      <c r="H260">
+        <v>0.08</v>
+      </c>
+      <c r="I260" s="55">
+        <f t="shared" si="10"/>
+        <v>0.10285714285714287</v>
       </c>
       <c r="T260">
         <v>104</v>
@@ -15885,6 +15587,13 @@
       </c>
     </row>
     <row r="261" spans="2:27">
+      <c r="H261">
+        <v>0.09</v>
+      </c>
+      <c r="I261" s="55">
+        <f t="shared" si="10"/>
+        <v>0.10857142857142858</v>
+      </c>
       <c r="T261">
         <v>107</v>
       </c>
@@ -15911,18 +15620,12 @@
       </c>
     </row>
     <row r="262" spans="2:27">
-      <c r="B262" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C262" s="40">
-        <f>P33</f>
-        <v>0.4</v>
-      </c>
-      <c r="H262" t="s">
-        <v>71</v>
-      </c>
-      <c r="I262" t="s">
-        <v>72</v>
+      <c r="H262">
+        <v>0.1</v>
+      </c>
+      <c r="I262" s="55">
+        <f t="shared" si="10"/>
+        <v>0.1142857142857143</v>
       </c>
       <c r="T262">
         <v>111</v>
@@ -15950,18 +15653,12 @@
       </c>
     </row>
     <row r="263" spans="2:27">
-      <c r="B263" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C263" s="40">
-        <f>P55</f>
-        <v>3</v>
-      </c>
-      <c r="H263" t="s">
-        <v>29</v>
-      </c>
-      <c r="I263" t="s">
-        <v>34</v>
+      <c r="H263">
+        <v>0.11</v>
+      </c>
+      <c r="I263" s="55">
+        <f t="shared" si="10"/>
+        <v>0.12000000000000001</v>
       </c>
       <c r="T263">
         <v>115</v>
@@ -15989,18 +15686,12 @@
       </c>
     </row>
     <row r="264" spans="2:27">
-      <c r="B264" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C264" s="40">
-        <f>P57</f>
-        <v>0.6</v>
-      </c>
       <c r="H264">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="I264" s="55">
-        <v>6.2857142857142861E-2</v>
+        <f t="shared" si="10"/>
+        <v>0.12571428571428572</v>
       </c>
       <c r="T264">
         <v>116</v>
@@ -16028,19 +15719,12 @@
       </c>
     </row>
     <row r="265" spans="2:27">
-      <c r="B265" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C265" s="40">
-        <f>Q85</f>
-        <v>1</v>
-      </c>
       <c r="H265">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="I265" s="55">
-        <f>IF(H265&lt;$C$264/3,   ($C$265*$C$262/$C$266)*(1+(3*($C$263-1)*H265/$C$264)),   IF(H265&lt;=$C$264,   $C$265*$C$262*$C$263/$C$266,   $C$265*$C$262*$C$263/$C$266*($C$264/H265)^(2/3)   ))</f>
-        <v>6.8571428571428575E-2</v>
+        <f t="shared" si="10"/>
+        <v>0.13142857142857142</v>
       </c>
       <c r="T265">
         <v>120</v>
@@ -16068,19 +15752,12 @@
       </c>
     </row>
     <row r="266" spans="2:27">
-      <c r="B266" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C266" s="40">
-        <f>P99</f>
-        <v>7</v>
-      </c>
       <c r="H266">
-        <v>0.03</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="I266" s="55">
-        <f t="shared" ref="I265:I328" si="10">IF(H266&lt;$C$264/3,   ($C$265*$C$262/$C$266)*(1+(3*($C$263-1)*H266/$C$264)),   IF(H266&lt;=$C$264,   $C$265*$C$262*$C$263/$C$266,   $C$265*$C$262*$C$263/$C$266*($C$264/H266)^(2/3)   ))</f>
-        <v>7.4285714285714288E-2</v>
+        <f t="shared" si="10"/>
+        <v>0.13714285714285718</v>
       </c>
       <c r="T266">
         <v>121</v>
@@ -16107,20 +15784,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="2:27">
-      <c r="B267" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C267" s="40">
-        <f>P97</f>
-        <v>6</v>
-      </c>
+    <row r="267" spans="8:27">
       <c r="H267">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="I267" s="55">
         <f t="shared" si="10"/>
-        <v>0.08</v>
+        <v>0.14285714285714288</v>
       </c>
       <c r="T267">
         <v>122</v>
@@ -16147,13 +15817,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="2:27">
+    <row r="268" spans="8:27">
       <c r="H268">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="I268" s="55">
         <f t="shared" si="10"/>
-        <v>8.5714285714285715E-2</v>
+        <v>0.14857142857142858</v>
       </c>
       <c r="T268">
         <v>124</v>
@@ -16180,13 +15850,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="2:27">
+    <row r="269" spans="8:27">
       <c r="H269">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="I269" s="55">
         <f t="shared" si="10"/>
-        <v>9.1428571428571442E-2</v>
+        <v>0.1542857142857143</v>
       </c>
       <c r="T269">
         <v>125</v>
@@ -16213,13 +15883,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="2:27">
+    <row r="270" spans="8:27">
       <c r="H270">
-        <v>7.0000000000000007E-2</v>
+        <v>0.18</v>
       </c>
       <c r="I270" s="55">
         <f t="shared" si="10"/>
-        <v>9.7142857142857156E-2</v>
+        <v>0.16000000000000003</v>
       </c>
       <c r="T270">
         <v>126</v>
@@ -16246,13 +15916,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="2:27">
+    <row r="271" spans="8:27">
       <c r="H271">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="I271" s="55">
         <f t="shared" si="10"/>
-        <v>0.10285714285714287</v>
+        <v>0.16571428571428576</v>
       </c>
       <c r="T271">
         <v>127</v>
@@ -16279,13 +15949,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="2:27">
+    <row r="272" spans="8:27">
       <c r="H272">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="I272" s="55">
         <f t="shared" si="10"/>
-        <v>0.10857142857142858</v>
+        <v>0.17142857142857146</v>
       </c>
       <c r="T272">
         <v>128</v>
@@ -16312,13 +15982,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="2:27">
+    <row r="273" spans="8:27">
       <c r="H273">
-        <v>0.1</v>
+        <v>0.21</v>
       </c>
       <c r="I273" s="55">
         <f t="shared" si="10"/>
-        <v>0.1142857142857143</v>
+        <v>0.17142857142857146</v>
       </c>
       <c r="T273">
         <v>130</v>
@@ -16345,13 +16015,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="2:27">
+    <row r="274" spans="8:27">
       <c r="H274">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="I274" s="55">
         <f t="shared" si="10"/>
-        <v>0.12000000000000001</v>
+        <v>0.17142857142857146</v>
       </c>
       <c r="T274">
         <v>131</v>
@@ -16378,13 +16048,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="2:27">
+    <row r="275" spans="8:27">
       <c r="H275">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="I275" s="55">
         <f t="shared" si="10"/>
-        <v>0.12571428571428572</v>
+        <v>0.17142857142857146</v>
       </c>
       <c r="T275">
         <v>132</v>
@@ -16411,13 +16081,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="2:27">
+    <row r="276" spans="8:27">
       <c r="H276">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="I276" s="55">
         <f t="shared" si="10"/>
-        <v>0.13142857142857142</v>
+        <v>0.17142857142857146</v>
+      </c>
+      <c r="K276">
+        <v>0.5</v>
+      </c>
+      <c r="L276">
+        <v>0</v>
       </c>
       <c r="T276">
         <v>133</v>
@@ -16444,13 +16120,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="2:27">
+    <row r="277" spans="8:27">
       <c r="H277">
-        <v>0.14000000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="I277" s="55">
         <f t="shared" si="10"/>
-        <v>0.13714285714285718</v>
+        <v>0.17142857142857146</v>
+      </c>
+      <c r="K277">
+        <v>0.5</v>
+      </c>
+      <c r="L277">
+        <v>0.33</v>
       </c>
       <c r="T277">
         <v>135</v>
@@ -16479,11 +16161,11 @@
     </row>
     <row r="278" spans="8:27">
       <c r="H278">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="I278" s="55">
         <f t="shared" si="10"/>
-        <v>0.14285714285714288</v>
+        <v>0.17142857142857146</v>
       </c>
       <c r="T278">
         <v>136</v>
@@ -16512,11 +16194,17 @@
     </row>
     <row r="279" spans="8:27">
       <c r="H279">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="I279" s="55">
         <f t="shared" si="10"/>
-        <v>0.14857142857142858</v>
+        <v>0.17142857142857146</v>
+      </c>
+      <c r="K279">
+        <v>0.71</v>
+      </c>
+      <c r="L279">
+        <v>0</v>
       </c>
       <c r="T279">
         <v>137</v>
@@ -16545,11 +16233,17 @@
     </row>
     <row r="280" spans="8:27">
       <c r="H280">
-        <v>0.17</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I280" s="55">
         <f t="shared" si="10"/>
-        <v>0.1542857142857143</v>
+        <v>0.17142857142857146</v>
+      </c>
+      <c r="K280">
+        <v>0.71</v>
+      </c>
+      <c r="L280">
+        <v>0.26</v>
       </c>
       <c r="T280">
         <v>138</v>
@@ -16578,11 +16272,11 @@
     </row>
     <row r="281" spans="8:27">
       <c r="H281">
-        <v>0.18</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I281" s="55">
         <f t="shared" si="10"/>
-        <v>0.16000000000000003</v>
+        <v>0.17142857142857146</v>
       </c>
       <c r="T281">
         <v>140</v>
@@ -16611,21 +16305,33 @@
     </row>
     <row r="282" spans="8:27">
       <c r="H282">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="I282" s="55">
         <f t="shared" si="10"/>
-        <v>0.16571428571428576</v>
+        <v>0.17142857142857146</v>
+      </c>
+      <c r="K282">
+        <v>0.94</v>
+      </c>
+      <c r="L282">
+        <v>0</v>
       </c>
     </row>
     <row r="283" spans="8:27">
       <c r="H283">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="I283" s="55">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
+      <c r="K283">
+        <v>0.94</v>
+      </c>
+      <c r="L283">
+        <v>0.217</v>
+      </c>
       <c r="V283">
         <f>SUM(V190:V281)</f>
         <v>-96.689999999999955</v>
@@ -16633,7 +16339,7 @@
     </row>
     <row r="284" spans="8:27">
       <c r="H284">
-        <v>0.21</v>
+        <v>0.32</v>
       </c>
       <c r="I284" s="55">
         <f t="shared" si="10"/>
@@ -16642,7 +16348,7 @@
     </row>
     <row r="285" spans="8:27">
       <c r="H285">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="I285" s="55">
         <f t="shared" si="10"/>
@@ -16651,7 +16357,7 @@
     </row>
     <row r="286" spans="8:27">
       <c r="H286">
-        <v>0.23</v>
+        <v>0.34</v>
       </c>
       <c r="I286" s="55">
         <f t="shared" si="10"/>
@@ -16660,37 +16366,25 @@
     </row>
     <row r="287" spans="8:27">
       <c r="H287">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="I287" s="55">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
-      <c r="K287">
-        <v>0.5</v>
-      </c>
-      <c r="L287">
-        <v>0</v>
-      </c>
     </row>
     <row r="288" spans="8:27">
       <c r="H288">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="I288" s="55">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
-      <c r="K288">
-        <v>0.5</v>
-      </c>
-      <c r="L288">
-        <v>0.33</v>
-      </c>
     </row>
     <row r="289" spans="8:27">
       <c r="H289">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="I289" s="55">
         <f t="shared" si="10"/>
@@ -16699,37 +16393,25 @@
     </row>
     <row r="290" spans="8:27">
       <c r="H290">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="I290" s="55">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
-      <c r="K290">
-        <v>0.71</v>
-      </c>
-      <c r="L290">
-        <v>0</v>
-      </c>
     </row>
     <row r="291" spans="8:27">
       <c r="H291">
-        <v>0.28000000000000003</v>
+        <v>0.39</v>
       </c>
       <c r="I291" s="55">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
-      <c r="K291">
-        <v>0.71</v>
-      </c>
-      <c r="L291">
-        <v>0.26</v>
-      </c>
     </row>
     <row r="292" spans="8:27">
       <c r="H292">
-        <v>0.28999999999999998</v>
+        <v>0.4</v>
       </c>
       <c r="I292" s="55">
         <f t="shared" si="10"/>
@@ -16738,37 +16420,25 @@
     </row>
     <row r="293" spans="8:27">
       <c r="H293">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="I293" s="55">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
-      <c r="K293">
-        <v>0.94</v>
-      </c>
-      <c r="L293">
-        <v>0</v>
-      </c>
     </row>
     <row r="294" spans="8:27">
       <c r="H294">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="I294" s="55">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
-      <c r="K294">
-        <v>0.94</v>
-      </c>
-      <c r="L294">
-        <v>0.217</v>
-      </c>
     </row>
     <row r="295" spans="8:27">
       <c r="H295">
-        <v>0.32</v>
+        <v>0.43</v>
       </c>
       <c r="I295" s="55">
         <f t="shared" si="10"/>
@@ -16777,7 +16447,7 @@
     </row>
     <row r="296" spans="8:27">
       <c r="H296">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="I296" s="55">
         <f t="shared" si="10"/>
@@ -16786,7 +16456,7 @@
     </row>
     <row r="297" spans="8:27">
       <c r="H297">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="I297" s="55">
         <f t="shared" si="10"/>
@@ -16795,7 +16465,7 @@
     </row>
     <row r="298" spans="8:27">
       <c r="H298">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="I298" s="55">
         <f t="shared" si="10"/>
@@ -16804,7 +16474,7 @@
     </row>
     <row r="299" spans="8:27">
       <c r="H299">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="I299" s="55">
         <f t="shared" si="10"/>
@@ -16813,7 +16483,7 @@
     </row>
     <row r="300" spans="8:27">
       <c r="H300">
-        <v>0.37</v>
+        <v>0.48</v>
       </c>
       <c r="I300" s="55">
         <f t="shared" si="10"/>
@@ -16822,7 +16492,7 @@
     </row>
     <row r="301" spans="8:27">
       <c r="H301">
-        <v>0.38</v>
+        <v>0.49</v>
       </c>
       <c r="I301" s="55">
         <f t="shared" si="10"/>
@@ -16831,7 +16501,7 @@
     </row>
     <row r="302" spans="8:27">
       <c r="H302">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="I302" s="55">
         <f t="shared" si="10"/>
@@ -16840,7 +16510,7 @@
     </row>
     <row r="303" spans="8:27">
       <c r="H303">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="I303" s="55">
         <f t="shared" si="10"/>
@@ -16849,7 +16519,7 @@
     </row>
     <row r="304" spans="8:27">
       <c r="H304">
-        <v>0.41</v>
+        <v>0.52</v>
       </c>
       <c r="I304" s="55">
         <f t="shared" si="10"/>
@@ -16858,7 +16528,7 @@
     </row>
     <row r="305" spans="8:27">
       <c r="H305">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="I305" s="55">
         <f t="shared" si="10"/>
@@ -16867,7 +16537,7 @@
     </row>
     <row r="306" spans="8:27">
       <c r="H306">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="I306" s="55">
         <f t="shared" si="10"/>
@@ -16876,7 +16546,7 @@
     </row>
     <row r="307" spans="8:27">
       <c r="H307">
-        <v>0.44</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I307" s="55">
         <f t="shared" si="10"/>
@@ -16885,7 +16555,7 @@
     </row>
     <row r="308" spans="8:27">
       <c r="H308">
-        <v>0.45</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I308" s="55">
         <f t="shared" si="10"/>
@@ -16894,7 +16564,7 @@
     </row>
     <row r="309" spans="8:27">
       <c r="H309">
-        <v>0.46</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I309" s="55">
         <f t="shared" si="10"/>
@@ -16903,7 +16573,7 @@
     </row>
     <row r="310" spans="8:27">
       <c r="H310">
-        <v>0.47</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I310" s="55">
         <f t="shared" si="10"/>
@@ -16912,7 +16582,7 @@
     </row>
     <row r="311" spans="8:27">
       <c r="H311">
-        <v>0.48</v>
+        <v>0.59</v>
       </c>
       <c r="I311" s="55">
         <f t="shared" si="10"/>
@@ -16921,7 +16591,7 @@
     </row>
     <row r="312" spans="8:27">
       <c r="H312">
-        <v>0.49</v>
+        <v>0.6</v>
       </c>
       <c r="I312" s="55">
         <f t="shared" si="10"/>
@@ -16930,2259 +16600,2160 @@
     </row>
     <row r="313" spans="8:27">
       <c r="H313">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="I313" s="55">
         <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
+        <v>0.16954987852001016</v>
       </c>
     </row>
     <row r="314" spans="8:27">
       <c r="H314">
-        <v>0.51</v>
+        <v>0.62</v>
       </c>
       <c r="I314" s="55">
         <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
-    </row>
-    <row r="315" spans="8:27">
+        <v>0.1677218252289068</v>
+      </c>
+    </row>
+    <row r="315" spans="8:9">
       <c r="H315">
-        <v>0.52</v>
+        <v>0.63</v>
       </c>
       <c r="I315" s="55">
         <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
-    </row>
-    <row r="316" spans="8:27">
+        <v>0.16594226233711895</v>
+      </c>
+    </row>
+    <row r="316" spans="8:9">
       <c r="H316">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="I316" s="55">
         <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
-    </row>
-    <row r="317" spans="8:27">
+        <v>0.16420916408433284</v>
+      </c>
+    </row>
+    <row r="317" spans="8:9">
       <c r="H317">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="I317" s="55">
         <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
-    </row>
-    <row r="318" spans="8:27">
+        <v>0.16252061928129335</v>
+      </c>
+    </row>
+    <row r="318" spans="8:9">
       <c r="H318">
-        <v>0.55000000000000004</v>
+        <v>0.66</v>
       </c>
       <c r="I318" s="55">
-        <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
-    </row>
-    <row r="319" spans="8:27">
+        <f t="shared" ref="I318:I381" si="11">IF(H318&lt;$C$253/3,   ($C$254*$C$251/$C$255)*(1+(3*($C$252-1)*H318/$C$253)),   IF(H318&lt;=$C$253,   $C$254*$C$251*$C$252/$C$255,   $C$254*$C$251*$C$252/$C$255*($C$253/H318)^(2/3)   ))</f>
+        <v>0.16087482318800531</v>
+      </c>
+    </row>
+    <row r="319" spans="8:9">
       <c r="H319">
-        <v>0.56000000000000005</v>
+        <v>0.67</v>
       </c>
       <c r="I319" s="55">
-        <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
-    </row>
-    <row r="320" spans="8:27">
+        <f t="shared" si="11"/>
+        <v>0.15927007008059582</v>
+      </c>
+    </row>
+    <row r="320" spans="8:9">
       <c r="H320">
-        <v>0.56999999999999995</v>
+        <v>0.68</v>
       </c>
       <c r="I320" s="55">
-        <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
-    </row>
-    <row r="321" spans="8:27">
+        <f t="shared" si="11"/>
+        <v>0.15770474643915294</v>
+      </c>
+    </row>
+    <row r="321" spans="8:9">
       <c r="H321">
-        <v>0.57999999999999996</v>
+        <v>0.69</v>
       </c>
       <c r="I321" s="55">
-        <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
-    </row>
-    <row r="322" spans="8:27">
+        <f t="shared" si="11"/>
+        <v>0.15617732469639467</v>
+      </c>
+    </row>
+    <row r="322" spans="8:9">
       <c r="H322">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="I322" s="55">
-        <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
-    </row>
-    <row r="323" spans="8:27">
+        <f t="shared" si="11"/>
+        <v>0.15468635749362564</v>
+      </c>
+    </row>
+    <row r="323" spans="8:9">
       <c r="H323">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="I323" s="55">
-        <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
-    </row>
-    <row r="324" spans="8:27">
+        <f t="shared" si="11"/>
+        <v>0.15323047239623552</v>
+      </c>
+    </row>
+    <row r="324" spans="8:9">
       <c r="H324">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="I324" s="55">
-        <f t="shared" si="10"/>
-        <v>0.16954987852001016</v>
-      </c>
-    </row>
-    <row r="325" spans="8:27">
+        <f t="shared" si="11"/>
+        <v>0.15180836702608733</v>
+      </c>
+    </row>
+    <row r="325" spans="8:9">
       <c r="H325">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="I325" s="55">
-        <f t="shared" si="10"/>
-        <v>0.1677218252289068</v>
+        <f t="shared" si="11"/>
+        <v>0.15041880457263548</v>
       </c>
     </row>
     <row r="326" spans="8:9">
       <c r="H326">
-        <v>0.63</v>
+        <v>0.74</v>
       </c>
       <c r="I326" s="55">
-        <f t="shared" si="10"/>
-        <v>0.16594226233711895</v>
+        <f t="shared" si="11"/>
+        <v>0.14906060964857532</v>
       </c>
     </row>
     <row r="327" spans="8:9">
       <c r="H327">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="I327" s="55">
-        <f t="shared" si="10"/>
-        <v>0.16420916408433284</v>
+        <f t="shared" si="11"/>
+        <v>0.1477326644593292</v>
       </c>
     </row>
     <row r="328" spans="8:9">
       <c r="H328">
-        <v>0.65</v>
+        <v>0.76</v>
       </c>
       <c r="I328" s="55">
-        <f t="shared" si="10"/>
-        <v>0.16252061928129335</v>
+        <f t="shared" si="11"/>
+        <v>0.14643390525877864</v>
       </c>
     </row>
     <row r="329" spans="8:9">
       <c r="H329">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="I329" s="55">
-        <f t="shared" ref="I329:I392" si="11">IF(H329&lt;$C$264/3,   ($C$265*$C$262/$C$266)*(1+(3*($C$263-1)*H329/$C$264)),   IF(H329&lt;=$C$264,   $C$265*$C$262*$C$263/$C$266,   $C$265*$C$262*$C$263/$C$266*($C$264/H329)^(2/3)   ))</f>
-        <v>0.16087482318800531</v>
+        <f t="shared" si="11"/>
+        <v>0.14516331906640431</v>
       </c>
     </row>
     <row r="330" spans="8:9">
       <c r="H330">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="I330" s="55">
         <f t="shared" si="11"/>
-        <v>0.15927007008059582</v>
+        <v>0.14391994062344254</v>
       </c>
     </row>
     <row r="331" spans="8:9">
       <c r="H331">
-        <v>0.68</v>
+        <v>0.79</v>
       </c>
       <c r="I331" s="55">
         <f t="shared" si="11"/>
-        <v>0.15770474643915294</v>
+        <v>0.1427028495678451</v>
       </c>
     </row>
     <row r="332" spans="8:9">
       <c r="H332">
-        <v>0.69</v>
+        <v>0.8</v>
       </c>
       <c r="I332" s="55">
         <f t="shared" si="11"/>
-        <v>0.15617732469639467</v>
+        <v>0.14151116780976972</v>
       </c>
     </row>
     <row r="333" spans="8:9">
       <c r="H333">
-        <v>0.7</v>
+        <v>0.81</v>
       </c>
       <c r="I333" s="55">
         <f t="shared" si="11"/>
-        <v>0.15468635749362564</v>
+        <v>0.14034405709106237</v>
       </c>
     </row>
     <row r="334" spans="8:9">
       <c r="H334">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="I334" s="55">
         <f t="shared" si="11"/>
-        <v>0.15323047239623552</v>
+        <v>0.13920071671374129</v>
       </c>
     </row>
     <row r="335" spans="8:9">
       <c r="H335">
-        <v>0.72</v>
+        <v>0.83</v>
       </c>
       <c r="I335" s="55">
         <f t="shared" si="11"/>
-        <v>0.15180836702608733</v>
+        <v>0.13808038142388113</v>
       </c>
     </row>
     <row r="336" spans="8:9">
       <c r="H336">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="I336" s="55">
         <f t="shared" si="11"/>
-        <v>0.15041880457263548</v>
+        <v>0.13698231943853842</v>
       </c>
     </row>
     <row r="337" spans="8:9">
       <c r="H337">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="I337" s="55">
         <f t="shared" si="11"/>
-        <v>0.14906060964857532</v>
+        <v>0.13590583060447733</v>
       </c>
     </row>
     <row r="338" spans="8:9">
       <c r="H338">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="I338" s="55">
         <f t="shared" si="11"/>
-        <v>0.1477326644593292</v>
+        <v>0.13485024467845858</v>
       </c>
     </row>
     <row r="339" spans="8:9">
       <c r="H339">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="I339" s="55">
         <f t="shared" si="11"/>
-        <v>0.14643390525877864</v>
+        <v>0.13381491971975773</v>
       </c>
     </row>
     <row r="340" spans="8:9">
       <c r="H340">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="I340" s="55">
         <f t="shared" si="11"/>
-        <v>0.14516331906640431</v>
+        <v>0.13279924058639495</v>
       </c>
     </row>
     <row r="341" spans="8:9">
       <c r="H341">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="I341" s="55">
         <f t="shared" si="11"/>
-        <v>0.14391994062344254</v>
+        <v>0.131802617527292</v>
       </c>
     </row>
     <row r="342" spans="8:9">
       <c r="H342">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="I342" s="55">
         <f t="shared" si="11"/>
-        <v>0.1427028495678451</v>
+        <v>0.13082448486323794</v>
       </c>
     </row>
     <row r="343" spans="8:9">
       <c r="H343">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="I343" s="55">
         <f t="shared" si="11"/>
-        <v>0.14151116780976972</v>
+        <v>0.12986429975014538</v>
       </c>
     </row>
     <row r="344" spans="8:9">
       <c r="H344">
-        <v>0.81</v>
+        <v>0.92</v>
       </c>
       <c r="I344" s="55">
         <f t="shared" si="11"/>
-        <v>0.14034405709106237</v>
+        <v>0.1289215410186223</v>
       </c>
     </row>
     <row r="345" spans="8:9">
       <c r="H345">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="I345" s="55">
         <f t="shared" si="11"/>
-        <v>0.13920071671374129</v>
+        <v>0.12799570808438024</v>
       </c>
     </row>
     <row r="346" spans="8:9">
       <c r="H346">
-        <v>0.83</v>
+        <v>0.94</v>
       </c>
       <c r="I346" s="55">
         <f t="shared" si="11"/>
-        <v>0.13808038142388113</v>
+        <v>0.12708631992444461</v>
       </c>
     </row>
     <row r="347" spans="8:9">
       <c r="H347">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="I347" s="55">
         <f t="shared" si="11"/>
-        <v>0.13698231943853842</v>
+        <v>0.126192914114542</v>
       </c>
     </row>
     <row r="348" spans="8:9">
       <c r="H348">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="I348" s="55">
         <f t="shared" si="11"/>
-        <v>0.13590583060447733</v>
+        <v>0.12531504592340856</v>
       </c>
     </row>
     <row r="349" spans="8:9">
       <c r="H349">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="I349" s="55">
         <f t="shared" si="11"/>
-        <v>0.13485024467845858</v>
+        <v>0.12445228746010001</v>
       </c>
     </row>
     <row r="350" spans="8:9">
       <c r="H350">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="I350" s="55">
         <f t="shared" si="11"/>
-        <v>0.13381491971975773</v>
+        <v>0.123604226870692</v>
       </c>
     </row>
     <row r="351" spans="8:9">
       <c r="H351">
-        <v>0.88</v>
+        <v>0.99</v>
       </c>
       <c r="I351" s="55">
         <f t="shared" si="11"/>
-        <v>0.13279924058639495</v>
+        <v>0.12277046758103911</v>
       </c>
     </row>
     <row r="352" spans="8:9">
       <c r="H352">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="I352" s="55">
         <f t="shared" si="11"/>
-        <v>0.131802617527292</v>
+        <v>0.12195062758251644</v>
       </c>
     </row>
     <row r="353" spans="8:9">
       <c r="H353">
-        <v>0.9</v>
+        <v>1.01</v>
       </c>
       <c r="I353" s="55">
         <f t="shared" si="11"/>
-        <v>0.13082448486323794</v>
+        <v>0.12114433875790227</v>
       </c>
     </row>
     <row r="354" spans="8:9">
       <c r="H354">
-        <v>0.91</v>
+        <v>1.02</v>
       </c>
       <c r="I354" s="55">
         <f t="shared" si="11"/>
-        <v>0.12986429975014538</v>
+        <v>0.1203512462447735</v>
       </c>
     </row>
     <row r="355" spans="8:9">
       <c r="H355">
-        <v>0.92</v>
+        <v>1.03</v>
       </c>
       <c r="I355" s="55">
         <f t="shared" si="11"/>
-        <v>0.1289215410186223</v>
+        <v>0.11957100783398215</v>
       </c>
     </row>
     <row r="356" spans="8:9">
       <c r="H356">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="I356" s="55">
         <f t="shared" si="11"/>
-        <v>0.12799570808438024</v>
+        <v>0.11880329340096042</v>
       </c>
     </row>
     <row r="357" spans="8:9">
       <c r="H357">
-        <v>0.94</v>
+        <v>1.05</v>
       </c>
       <c r="I357" s="55">
         <f t="shared" si="11"/>
-        <v>0.12708631992444461</v>
+        <v>0.11804778436776639</v>
       </c>
     </row>
     <row r="358" spans="8:9">
       <c r="H358">
-        <v>0.95</v>
+        <v>1.06</v>
       </c>
       <c r="I358" s="55">
         <f t="shared" si="11"/>
-        <v>0.126192914114542</v>
+        <v>0.11730417319393414</v>
       </c>
     </row>
     <row r="359" spans="8:9">
       <c r="H359">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="I359" s="55">
         <f t="shared" si="11"/>
-        <v>0.12531504592340856</v>
+        <v>0.11657216289433078</v>
       </c>
     </row>
     <row r="360" spans="8:9">
       <c r="H360">
-        <v>0.97</v>
+        <v>1.08</v>
       </c>
       <c r="I360" s="55">
         <f t="shared" si="11"/>
-        <v>0.12445228746010001</v>
+        <v>0.1158514665823505</v>
       </c>
     </row>
     <row r="361" spans="8:9">
       <c r="H361">
-        <v>0.98</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I361" s="55">
         <f t="shared" si="11"/>
-        <v>0.123604226870692</v>
+        <v>0.11514180703689374</v>
       </c>
     </row>
     <row r="362" spans="8:9">
       <c r="H362">
-        <v>0.99</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I362" s="55">
         <f t="shared" si="11"/>
-        <v>0.12277046758103911</v>
+        <v>0.11444291629168775</v>
       </c>
     </row>
     <row r="363" spans="8:9">
       <c r="H363">
-        <v>1</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="I363" s="55">
         <f t="shared" si="11"/>
-        <v>0.12195062758251644</v>
+        <v>0.1137545352456045</v>
       </c>
     </row>
     <row r="364" spans="8:9">
       <c r="H364">
-        <v>1.01</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="I364" s="55">
         <f t="shared" si="11"/>
-        <v>0.12114433875790227</v>
+        <v>0.11307641329272453</v>
       </c>
     </row>
     <row r="365" spans="8:9">
       <c r="H365">
-        <v>1.02</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="I365" s="55">
         <f t="shared" si="11"/>
-        <v>0.1203512462447735</v>
+        <v>0.11240830797097949</v>
       </c>
     </row>
     <row r="366" spans="8:9">
       <c r="H366">
-        <v>1.03</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="I366" s="55">
         <f t="shared" si="11"/>
-        <v>0.11957100783398215</v>
+        <v>0.11174998462828611</v>
       </c>
     </row>
     <row r="367" spans="8:9">
       <c r="H367">
-        <v>1.04</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="I367" s="55">
         <f t="shared" si="11"/>
-        <v>0.11880329340096042</v>
+        <v>0.11110121610515532</v>
       </c>
     </row>
     <row r="368" spans="8:9">
       <c r="H368">
-        <v>1.05</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="I368" s="55">
         <f t="shared" si="11"/>
-        <v>0.11804778436776639</v>
+        <v>0.11046178243282875</v>
       </c>
     </row>
     <row r="369" spans="8:9">
       <c r="H369">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="I369" s="55">
         <f t="shared" si="11"/>
-        <v>0.11730417319393414</v>
+        <v>0.10983147054605637</v>
       </c>
     </row>
     <row r="370" spans="8:9">
       <c r="H370">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="I370" s="55">
         <f t="shared" si="11"/>
-        <v>0.11657216289433078</v>
+        <v>0.10921007400968709</v>
       </c>
     </row>
     <row r="371" spans="8:9">
       <c r="H371">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="I371" s="55">
         <f t="shared" si="11"/>
-        <v>0.1158514665823505</v>
+        <v>0.10859739275829733</v>
       </c>
     </row>
     <row r="372" spans="8:9">
       <c r="H372">
-        <v>1.0900000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="I372" s="55">
         <f t="shared" si="11"/>
-        <v>0.11514180703689374</v>
+        <v>0.107993232848132</v>
       </c>
     </row>
     <row r="373" spans="8:9">
       <c r="H373">
-        <v>1.1000000000000001</v>
+        <v>1.21</v>
       </c>
       <c r="I373" s="55">
         <f t="shared" si="11"/>
-        <v>0.11444291629168775</v>
+        <v>0.10739740622067891</v>
       </c>
     </row>
     <row r="374" spans="8:9">
       <c r="H374">
-        <v>1.1100000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="I374" s="55">
         <f t="shared" si="11"/>
-        <v>0.1137545352456045</v>
+        <v>0.10680973047723971</v>
       </c>
     </row>
     <row r="375" spans="8:9">
       <c r="H375">
-        <v>1.1200000000000001</v>
+        <v>1.23</v>
       </c>
       <c r="I375" s="55">
         <f t="shared" si="11"/>
-        <v>0.11307641329272453</v>
+        <v>0.10623002866390084</v>
       </c>
     </row>
     <row r="376" spans="8:9">
       <c r="H376">
-        <v>1.1299999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="I376" s="55">
         <f t="shared" si="11"/>
-        <v>0.11240830797097949</v>
+        <v>0.10565812906634435</v>
       </c>
     </row>
     <row r="377" spans="8:9">
       <c r="H377">
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="I377" s="55">
         <f t="shared" si="11"/>
-        <v>0.11174998462828611</v>
+        <v>0.10509386501397301</v>
       </c>
     </row>
     <row r="378" spans="8:9">
       <c r="H378">
-        <v>1.1499999999999999</v>
+        <v>1.26</v>
       </c>
       <c r="I378" s="55">
         <f t="shared" si="11"/>
-        <v>0.11110121610515532</v>
+        <v>0.1045370746928567</v>
       </c>
     </row>
     <row r="379" spans="8:9">
       <c r="H379">
-        <v>1.1599999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="I379" s="55">
         <f t="shared" si="11"/>
-        <v>0.11046178243282875</v>
+        <v>0.10398760096703577</v>
       </c>
     </row>
     <row r="380" spans="8:9">
       <c r="H380">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="I380" s="55">
         <f t="shared" si="11"/>
-        <v>0.10983147054605637</v>
+        <v>0.10344529120774607</v>
       </c>
     </row>
     <row r="381" spans="8:9">
       <c r="H381">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="I381" s="55">
         <f t="shared" si="11"/>
-        <v>0.10921007400968709</v>
+        <v>0.10290999713015545</v>
       </c>
     </row>
     <row r="382" spans="8:9">
       <c r="H382">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="I382" s="55">
-        <f t="shared" si="11"/>
-        <v>0.10859739275829733</v>
+        <f t="shared" ref="I382:I445" si="12">IF(H382&lt;$C$253/3,   ($C$254*$C$251/$C$255)*(1+(3*($C$252-1)*H382/$C$253)),   IF(H382&lt;=$C$253,   $C$254*$C$251*$C$252/$C$255,   $C$254*$C$251*$C$252/$C$255*($C$253/H382)^(2/3)   ))</f>
+        <v>0.10238157463722605</v>
       </c>
     </row>
     <row r="383" spans="8:9">
       <c r="H383">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="I383" s="55">
-        <f t="shared" si="11"/>
-        <v>0.107993232848132</v>
+        <f t="shared" si="12"/>
+        <v>0.10185988367033932</v>
       </c>
     </row>
     <row r="384" spans="8:9">
       <c r="H384">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="I384" s="55">
-        <f t="shared" si="11"/>
-        <v>0.10739740622067891</v>
+        <f t="shared" si="12"/>
+        <v>0.10134478806634185</v>
       </c>
     </row>
     <row r="385" spans="8:9">
       <c r="H385">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="I385" s="55">
-        <f t="shared" si="11"/>
-        <v>0.10680973047723971</v>
+        <f t="shared" si="12"/>
+        <v>0.10083615542068967</v>
       </c>
     </row>
     <row r="386" spans="8:9">
       <c r="H386">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="I386" s="55">
-        <f t="shared" si="11"/>
-        <v>0.10623002866390084</v>
+        <f t="shared" si="12"/>
+        <v>0.10033385695638715</v>
       </c>
     </row>
     <row r="387" spans="8:9">
       <c r="H387">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="I387" s="55">
-        <f t="shared" si="11"/>
-        <v>0.10565812906634435</v>
+        <f t="shared" si="12"/>
+        <v>9.9837767398434168E-2</v>
       </c>
     </row>
     <row r="388" spans="8:9">
       <c r="H388">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="I388" s="55">
-        <f t="shared" si="11"/>
-        <v>0.10509386501397301</v>
+        <f t="shared" si="12"/>
+        <v>9.934776485351117E-2</v>
       </c>
     </row>
     <row r="389" spans="8:9">
       <c r="H389">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="I389" s="55">
-        <f t="shared" si="11"/>
-        <v>0.1045370746928567</v>
+        <f t="shared" si="12"/>
+        <v>9.8863730694646768E-2</v>
       </c>
     </row>
     <row r="390" spans="8:9">
       <c r="H390">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="I390" s="55">
-        <f t="shared" si="11"/>
-        <v>0.10398760096703577</v>
+        <f t="shared" si="12"/>
+        <v>9.8385549450627038E-2</v>
       </c>
     </row>
     <row r="391" spans="8:9">
       <c r="H391">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="I391" s="55">
-        <f t="shared" si="11"/>
-        <v>0.10344529120774607</v>
+        <f t="shared" si="12"/>
+        <v>9.7913108699918719E-2</v>
       </c>
     </row>
     <row r="392" spans="8:9">
       <c r="H392">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="I392" s="55">
-        <f t="shared" si="11"/>
-        <v>0.10290999713015545</v>
+        <f t="shared" si="12"/>
+        <v>9.7446298968891246E-2</v>
       </c>
     </row>
     <row r="393" spans="8:9">
       <c r="H393">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="I393" s="55">
-        <f t="shared" ref="I393:I456" si="12">IF(H393&lt;$C$264/3,   ($C$265*$C$262/$C$266)*(1+(3*($C$263-1)*H393/$C$264)),   IF(H393&lt;=$C$264,   $C$265*$C$262*$C$263/$C$266,   $C$265*$C$262*$C$263/$C$266*($C$264/H393)^(2/3)   ))</f>
-        <v>0.10238157463722605</v>
+        <f t="shared" si="12"/>
+        <v>9.6985013634134004E-2</v>
       </c>
     </row>
     <row r="394" spans="8:9">
       <c r="H394">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="I394" s="55">
         <f t="shared" si="12"/>
-        <v>0.10185988367033932</v>
+        <v>9.6529148828676206E-2</v>
       </c>
     </row>
     <row r="395" spans="8:9">
       <c r="H395">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="I395" s="55">
         <f t="shared" si="12"/>
-        <v>0.10134478806634185</v>
+        <v>9.6078603351927624E-2</v>
       </c>
     </row>
     <row r="396" spans="8:9">
       <c r="H396">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="I396" s="55">
         <f t="shared" si="12"/>
-        <v>0.10083615542068967</v>
+        <v>9.56332785831671E-2</v>
       </c>
     </row>
     <row r="397" spans="8:9">
       <c r="H397">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="I397" s="55">
         <f t="shared" si="12"/>
-        <v>0.10033385695638715</v>
+        <v>9.5193078398416328E-2</v>
       </c>
     </row>
     <row r="398" spans="8:9">
       <c r="H398">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="I398" s="55">
         <f t="shared" si="12"/>
-        <v>9.9837767398434168E-2</v>
+        <v>9.4757909090543324E-2</v>
       </c>
     </row>
     <row r="399" spans="8:9">
       <c r="H399">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="I399" s="55">
         <f t="shared" si="12"/>
-        <v>9.934776485351117E-2</v>
+        <v>9.432767929244959E-2</v>
       </c>
     </row>
     <row r="400" spans="8:9">
       <c r="H400">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="I400" s="55">
         <f t="shared" si="12"/>
-        <v>9.8863730694646768E-2</v>
+        <v>9.3902299903201439E-2</v>
       </c>
     </row>
     <row r="401" spans="8:9">
       <c r="H401">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="I401" s="55">
         <f t="shared" si="12"/>
-        <v>9.8385549450627038E-2</v>
+        <v>9.3481684016974015E-2</v>
       </c>
     </row>
     <row r="402" spans="8:9">
       <c r="H402">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="I402" s="55">
         <f t="shared" si="12"/>
-        <v>9.7913108699918719E-2</v>
+        <v>9.3065746854682524E-2</v>
       </c>
     </row>
     <row r="403" spans="8:9">
       <c r="H403">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="I403" s="55">
         <f t="shared" si="12"/>
-        <v>9.7446298968891246E-2</v>
+        <v>9.2654405698182091E-2</v>
       </c>
     </row>
     <row r="404" spans="8:9">
       <c r="H404">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="I404" s="55">
         <f t="shared" si="12"/>
-        <v>9.6985013634134004E-2</v>
+        <v>9.2247579826923401E-2</v>
       </c>
     </row>
     <row r="405" spans="8:9">
       <c r="H405">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="I405" s="55">
         <f t="shared" si="12"/>
-        <v>9.6529148828676206E-2</v>
+        <v>9.1845190456956952E-2</v>
       </c>
     </row>
     <row r="406" spans="8:9">
       <c r="H406">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="I406" s="55">
         <f t="shared" si="12"/>
-        <v>9.6078603351927624E-2</v>
+        <v>9.1447160682184309E-2</v>
       </c>
     </row>
     <row r="407" spans="8:9">
       <c r="H407">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="I407" s="55">
         <f t="shared" si="12"/>
-        <v>9.56332785831671E-2</v>
+        <v>9.105341541775934E-2</v>
       </c>
     </row>
     <row r="408" spans="8:9">
       <c r="H408">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="I408" s="55">
         <f t="shared" si="12"/>
-        <v>9.5193078398416328E-2</v>
+        <v>9.0663881345547773E-2</v>
       </c>
     </row>
     <row r="409" spans="8:9">
       <c r="H409">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="I409" s="55">
         <f t="shared" si="12"/>
-        <v>9.4757909090543324E-2</v>
+        <v>9.0278486861557219E-2</v>
       </c>
     </row>
     <row r="410" spans="8:9">
       <c r="H410">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="I410" s="55">
         <f t="shared" si="12"/>
-        <v>9.432767929244959E-2</v>
+        <v>8.9897162025254787E-2</v>
       </c>
     </row>
     <row r="411" spans="8:9">
       <c r="H411">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="I411" s="55">
         <f t="shared" si="12"/>
-        <v>9.3902299903201439E-2</v>
+        <v>8.9519838510692798E-2</v>
       </c>
     </row>
     <row r="412" spans="8:9">
       <c r="H412">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="I412" s="55">
         <f t="shared" si="12"/>
-        <v>9.3481684016974015E-2</v>
+        <v>8.9146449559367333E-2</v>
       </c>
     </row>
     <row r="413" spans="8:9">
       <c r="H413">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="I413" s="55">
         <f t="shared" si="12"/>
-        <v>9.3065746854682524E-2</v>
+        <v>8.8776929934737764E-2</v>
       </c>
     </row>
     <row r="414" spans="8:9">
       <c r="H414">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="I414" s="55">
         <f t="shared" si="12"/>
-        <v>9.2654405698182091E-2</v>
+        <v>8.8411215878338653E-2</v>
       </c>
     </row>
     <row r="415" spans="8:9">
       <c r="H415">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="I415" s="55">
         <f t="shared" si="12"/>
-        <v>9.2247579826923401E-2</v>
+        <v>8.8049245067419249E-2</v>
       </c>
     </row>
     <row r="416" spans="8:9">
       <c r="H416">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="I416" s="55">
         <f t="shared" si="12"/>
-        <v>9.1845190456956952E-2</v>
+        <v>8.7690956574047879E-2</v>
       </c>
     </row>
     <row r="417" spans="8:9">
       <c r="H417">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="I417" s="55">
         <f t="shared" si="12"/>
-        <v>9.1447160682184309E-2</v>
+        <v>8.7336290825622484E-2</v>
       </c>
     </row>
     <row r="418" spans="8:9">
       <c r="H418">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="I418" s="55">
         <f t="shared" si="12"/>
-        <v>9.105341541775934E-2</v>
+        <v>8.6985189566730431E-2</v>
       </c>
     </row>
     <row r="419" spans="8:9">
       <c r="H419">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="I419" s="55">
         <f t="shared" si="12"/>
-        <v>9.0663881345547773E-2</v>
+        <v>8.6637595822303889E-2</v>
       </c>
     </row>
     <row r="420" spans="8:9">
       <c r="H420">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="I420" s="55">
         <f t="shared" si="12"/>
-        <v>9.0278486861557219E-2</v>
+        <v>8.6293453862019115E-2</v>
       </c>
     </row>
     <row r="421" spans="8:9">
       <c r="H421">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="I421" s="55">
         <f t="shared" si="12"/>
-        <v>8.9897162025254787E-2</v>
+        <v>8.5952709165890706E-2</v>
       </c>
     </row>
     <row r="422" spans="8:9">
       <c r="H422">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="I422" s="55">
         <f t="shared" si="12"/>
-        <v>8.9519838510692798E-2</v>
+        <v>8.5615308391013945E-2</v>
       </c>
     </row>
     <row r="423" spans="8:9">
       <c r="H423">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="I423" s="55">
         <f t="shared" si="12"/>
-        <v>8.9146449559367333E-2</v>
+        <v>8.5281199339410016E-2</v>
       </c>
     </row>
     <row r="424" spans="8:9">
       <c r="H424">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="I424" s="55">
         <f t="shared" si="12"/>
-        <v>8.8776929934737764E-2</v>
+        <v>8.4950330926932036E-2</v>
       </c>
     </row>
     <row r="425" spans="8:9">
       <c r="H425">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="I425" s="55">
         <f t="shared" si="12"/>
-        <v>8.8411215878338653E-2</v>
+        <v>8.462265315319023E-2</v>
       </c>
     </row>
     <row r="426" spans="8:9">
       <c r="H426">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="I426" s="55">
         <f t="shared" si="12"/>
-        <v>8.8049245067419249E-2</v>
+        <v>8.4298117072457671E-2</v>
       </c>
     </row>
     <row r="427" spans="8:9">
       <c r="H427">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="I427" s="55">
         <f t="shared" si="12"/>
-        <v>8.7690956574047879E-2</v>
+        <v>8.3976674765518997E-2</v>
       </c>
     </row>
     <row r="428" spans="8:9">
       <c r="H428">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="I428" s="55">
         <f t="shared" si="12"/>
-        <v>8.7336290825622484E-2</v>
+        <v>8.3658279312426295E-2</v>
       </c>
     </row>
     <row r="429" spans="8:9">
       <c r="H429">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="I429" s="55">
         <f t="shared" si="12"/>
-        <v>8.6985189566730431E-2</v>
+        <v>8.3342884766128181E-2</v>
       </c>
     </row>
     <row r="430" spans="8:9">
       <c r="H430">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="I430" s="55">
         <f t="shared" si="12"/>
-        <v>8.6637595822303889E-2</v>
+        <v>8.3030446126939078E-2</v>
       </c>
     </row>
     <row r="431" spans="8:9">
       <c r="H431">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="I431" s="55">
         <f t="shared" si="12"/>
-        <v>8.6293453862019115E-2</v>
+        <v>8.2720919317817471E-2</v>
       </c>
     </row>
     <row r="432" spans="8:9">
       <c r="H432">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="I432" s="55">
         <f t="shared" si="12"/>
-        <v>8.5952709165890706E-2</v>
+        <v>8.2414261160423344E-2</v>
       </c>
     </row>
     <row r="433" spans="8:9">
       <c r="H433">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="I433" s="55">
         <f t="shared" si="12"/>
-        <v>8.5615308391013945E-2</v>
+        <v>8.2110429351925696E-2</v>
       </c>
     </row>
     <row r="434" spans="8:9">
       <c r="H434">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="I434" s="55">
         <f t="shared" si="12"/>
-        <v>8.5281199339410016E-2</v>
+        <v>8.180938244253283E-2</v>
       </c>
     </row>
     <row r="435" spans="8:9">
       <c r="H435">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="I435" s="55">
         <f t="shared" si="12"/>
-        <v>8.4950330926932036E-2</v>
+        <v>8.1511079813719314E-2</v>
       </c>
     </row>
     <row r="436" spans="8:9">
       <c r="H436">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="I436" s="55">
         <f t="shared" si="12"/>
-        <v>8.462265315319023E-2</v>
+        <v>8.1215481657123792E-2</v>
       </c>
     </row>
     <row r="437" spans="8:9">
       <c r="H437">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="I437" s="55">
         <f t="shared" si="12"/>
-        <v>8.4298117072457671E-2</v>
+        <v>8.0922548954093912E-2</v>
       </c>
     </row>
     <row r="438" spans="8:9">
       <c r="H438">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="I438" s="55">
         <f t="shared" si="12"/>
-        <v>8.3976674765518997E-2</v>
+        <v>8.063224345585504E-2</v>
       </c>
     </row>
     <row r="439" spans="8:9">
       <c r="H439">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="I439" s="55">
         <f t="shared" si="12"/>
-        <v>8.3658279312426295E-2</v>
+        <v>8.0344527664280296E-2</v>
       </c>
     </row>
     <row r="440" spans="8:9">
       <c r="H440">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="I440" s="55">
         <f t="shared" si="12"/>
-        <v>8.3342884766128181E-2</v>
+        <v>8.0059364813240996E-2</v>
       </c>
     </row>
     <row r="441" spans="8:9">
       <c r="H441">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="I441" s="55">
         <f t="shared" si="12"/>
-        <v>8.3030446126939078E-2</v>
+        <v>7.9776718850516348E-2</v>
       </c>
     </row>
     <row r="442" spans="8:9">
       <c r="H442">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="I442" s="55">
         <f t="shared" si="12"/>
-        <v>8.2720919317817471E-2</v>
+        <v>7.9496554420243656E-2</v>
       </c>
     </row>
     <row r="443" spans="8:9">
       <c r="H443">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="I443" s="55">
         <f t="shared" si="12"/>
-        <v>8.2414261160423344E-2</v>
+        <v>7.9218836845889234E-2</v>
       </c>
     </row>
     <row r="444" spans="8:9">
       <c r="H444">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="I444" s="55">
         <f t="shared" si="12"/>
-        <v>8.2110429351925696E-2</v>
+        <v>7.8943532113722584E-2</v>
       </c>
     </row>
     <row r="445" spans="8:9">
       <c r="H445">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="I445" s="55">
         <f t="shared" si="12"/>
-        <v>8.180938244253283E-2</v>
+        <v>7.8670606856776112E-2</v>
       </c>
     </row>
     <row r="446" spans="8:9">
       <c r="H446">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="I446" s="55">
-        <f t="shared" si="12"/>
-        <v>8.1511079813719314E-2</v>
+        <f t="shared" ref="I446:I509" si="13">IF(H446&lt;$C$253/3,   ($C$254*$C$251/$C$255)*(1+(3*($C$252-1)*H446/$C$253)),   IF(H446&lt;=$C$253,   $C$254*$C$251*$C$252/$C$255,   $C$254*$C$251*$C$252/$C$255*($C$253/H446)^(2/3)   ))</f>
+        <v>7.8400028339273883E-2</v>
       </c>
     </row>
     <row r="447" spans="8:9">
       <c r="H447">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="I447" s="55">
-        <f t="shared" si="12"/>
-        <v>8.1215481657123792E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.8131764441513082E-2</v>
       </c>
     </row>
     <row r="448" spans="8:9">
       <c r="H448">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="I448" s="55">
-        <f t="shared" si="12"/>
-        <v>8.0922548954093912E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.7865783645183179E-2</v>
       </c>
     </row>
     <row r="449" spans="8:9">
       <c r="H449">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="I449" s="55">
-        <f t="shared" si="12"/>
-        <v>8.063224345585504E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.7602055019107566E-2</v>
       </c>
     </row>
     <row r="450" spans="8:9">
       <c r="H450">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="I450" s="55">
-        <f t="shared" si="12"/>
-        <v>8.0344527664280296E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.7340548205393655E-2</v>
       </c>
     </row>
     <row r="451" spans="8:9">
       <c r="H451">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="I451" s="55">
-        <f t="shared" si="12"/>
-        <v>8.0059364813240996E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.708123340597775E-2</v>
       </c>
     </row>
     <row r="452" spans="8:9">
       <c r="H452">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="I452" s="55">
-        <f t="shared" si="12"/>
-        <v>7.9776718850516348E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.6824081369551406E-2</v>
       </c>
     </row>
     <row r="453" spans="8:9">
       <c r="H453">
-        <v>1.9</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="I453" s="55">
-        <f t="shared" si="12"/>
-        <v>7.9496554420243656E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.6569063378856717E-2</v>
       </c>
     </row>
     <row r="454" spans="8:9">
       <c r="H454">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="I454" s="55">
-        <f t="shared" si="12"/>
-        <v>7.9218836845889234E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.6316151238338195E-2</v>
       </c>
     </row>
     <row r="455" spans="8:9">
       <c r="H455">
-        <v>1.92</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="I455" s="55">
-        <f t="shared" si="12"/>
-        <v>7.8943532113722584E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.6065317262139873E-2</v>
       </c>
     </row>
     <row r="456" spans="8:9">
       <c r="H456">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="I456" s="55">
-        <f t="shared" si="12"/>
-        <v>7.8670606856776112E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.5816534262435717E-2</v>
       </c>
     </row>
     <row r="457" spans="8:9">
       <c r="H457">
-        <v>1.94</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="I457" s="55">
-        <f t="shared" ref="I457:I520" si="13">IF(H457&lt;$C$264/3,   ($C$265*$C$262/$C$266)*(1+(3*($C$263-1)*H457/$C$264)),   IF(H457&lt;=$C$264,   $C$265*$C$262*$C$263/$C$266,   $C$265*$C$262*$C$263/$C$266*($C$264/H457)^(2/3)   ))</f>
-        <v>7.8400028339273883E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.5569775538083292E-2</v>
       </c>
     </row>
     <row r="458" spans="8:9">
       <c r="H458">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="I458" s="55">
         <f t="shared" si="13"/>
-        <v>7.8131764441513082E-2</v>
+        <v>7.532501486358946E-2</v>
       </c>
     </row>
     <row r="459" spans="8:9">
       <c r="H459">
-        <v>1.96</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="I459" s="55">
         <f t="shared" si="13"/>
-        <v>7.7865783645183179E-2</v>
+        <v>7.5082226478378589E-2</v>
       </c>
     </row>
     <row r="460" spans="8:9">
       <c r="H460">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="I460" s="55">
         <f t="shared" si="13"/>
-        <v>7.7602055019107566E-2</v>
+        <v>7.4841385076353351E-2</v>
       </c>
     </row>
     <row r="461" spans="8:9">
       <c r="H461">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="I461" s="55">
         <f t="shared" si="13"/>
-        <v>7.7340548205393655E-2</v>
+        <v>7.4602465795738634E-2</v>
       </c>
     </row>
     <row r="462" spans="8:9">
       <c r="H462">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="I462" s="55">
         <f t="shared" si="13"/>
-        <v>7.708123340597775E-2</v>
+        <v>7.436544420919991E-2</v>
       </c>
     </row>
     <row r="463" spans="8:9">
       <c r="H463">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="I463" s="55">
         <f t="shared" si="13"/>
-        <v>7.6824081369551406E-2</v>
+        <v>7.4130296314227115E-2</v>
       </c>
     </row>
     <row r="464" spans="8:9">
       <c r="H464">
-        <v>2.0099999999999998</v>
+        <v>2.12</v>
       </c>
       <c r="I464" s="55">
         <f t="shared" si="13"/>
-        <v>7.6569063378856717E-2</v>
+        <v>7.3896998523775778E-2</v>
       </c>
     </row>
     <row r="465" spans="8:9">
       <c r="H465">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="I465" s="55">
         <f t="shared" si="13"/>
-        <v>7.6316151238338195E-2</v>
+        <v>7.3665527657157295E-2</v>
       </c>
     </row>
     <row r="466" spans="8:9">
       <c r="H466">
-        <v>2.0299999999999998</v>
+        <v>2.14</v>
       </c>
       <c r="I466" s="55">
         <f t="shared" si="13"/>
-        <v>7.6065317262139873E-2</v>
+        <v>7.3435860931170702E-2</v>
       </c>
     </row>
     <row r="467" spans="8:9">
       <c r="H467">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="I467" s="55">
         <f t="shared" si="13"/>
-        <v>7.5816534262435717E-2</v>
+        <v>7.3207975951468302E-2</v>
       </c>
     </row>
     <row r="468" spans="8:9">
       <c r="H468">
-        <v>2.0499999999999998</v>
+        <v>2.16</v>
       </c>
       <c r="I468" s="55">
         <f t="shared" si="13"/>
-        <v>7.5569775538083292E-2</v>
+        <v>7.2981850704147921E-2</v>
       </c>
     </row>
     <row r="469" spans="8:9">
       <c r="H469">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="I469" s="55">
         <f t="shared" si="13"/>
-        <v>7.532501486358946E-2</v>
+        <v>7.2757463547565099E-2</v>
       </c>
     </row>
     <row r="470" spans="8:9">
       <c r="H470">
-        <v>2.0699999999999998</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="I470" s="55">
         <f t="shared" si="13"/>
-        <v>7.5082226478378589E-2</v>
+        <v>7.2534793204358031E-2</v>
       </c>
     </row>
     <row r="471" spans="8:9">
       <c r="H471">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="I471" s="55">
         <f t="shared" si="13"/>
-        <v>7.4841385076353351E-2</v>
+        <v>7.231381875367919E-2</v>
       </c>
     </row>
     <row r="472" spans="8:9">
       <c r="H472">
-        <v>2.09</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I472" s="55">
         <f t="shared" si="13"/>
-        <v>7.4602465795738634E-2</v>
+        <v>7.2094519623627146E-2</v>
       </c>
     </row>
     <row r="473" spans="8:9">
       <c r="H473">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="I473" s="55">
         <f t="shared" si="13"/>
-        <v>7.436544420919991E-2</v>
+        <v>7.1876875583872596E-2</v>
       </c>
     </row>
     <row r="474" spans="8:9">
       <c r="H474">
-        <v>2.11</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="I474" s="55">
         <f t="shared" si="13"/>
-        <v>7.4130296314227115E-2</v>
+        <v>7.1660866738472703E-2</v>
       </c>
     </row>
     <row r="475" spans="8:9">
       <c r="H475">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="I475" s="55">
         <f t="shared" si="13"/>
-        <v>7.3896998523775778E-2</v>
+        <v>7.1446473518868236E-2</v>
       </c>
     </row>
     <row r="476" spans="8:9">
       <c r="H476">
-        <v>2.13</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I476" s="55">
         <f t="shared" si="13"/>
-        <v>7.3665527657157295E-2</v>
+        <v>7.123367667705803E-2</v>
       </c>
     </row>
     <row r="477" spans="8:9">
       <c r="H477">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="I477" s="55">
         <f t="shared" si="13"/>
-        <v>7.3435860931170702E-2</v>
+        <v>7.1022457278945364E-2</v>
       </c>
     </row>
     <row r="478" spans="8:9">
       <c r="H478">
-        <v>2.15</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="I478" s="55">
         <f t="shared" si="13"/>
-        <v>7.3207975951468302E-2</v>
+        <v>7.0812796697851343E-2</v>
       </c>
     </row>
     <row r="479" spans="8:9">
       <c r="H479">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="I479" s="55">
         <f t="shared" si="13"/>
-        <v>7.2981850704147921E-2</v>
+        <v>7.0604676608190434E-2</v>
       </c>
     </row>
     <row r="480" spans="8:9">
       <c r="H480">
-        <v>2.17</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="I480" s="55">
         <f t="shared" si="13"/>
-        <v>7.2757463547565099E-2</v>
+        <v>7.0398078979303086E-2</v>
       </c>
     </row>
     <row r="481" spans="8:9">
       <c r="H481">
-        <v>2.1800000000000002</v>
+        <v>2.29</v>
       </c>
       <c r="I481" s="55">
         <f t="shared" si="13"/>
-        <v>7.2534793204358031E-2</v>
+        <v>7.0192986069441285E-2</v>
       </c>
     </row>
     <row r="482" spans="8:9">
       <c r="H482">
-        <v>2.19</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="I482" s="55">
         <f t="shared" si="13"/>
-        <v>7.231381875367919E-2</v>
+        <v>6.9989380419902256E-2</v>
       </c>
     </row>
     <row r="483" spans="8:9">
       <c r="H483">
-        <v>2.2000000000000002</v>
+        <v>2.31</v>
       </c>
       <c r="I483" s="55">
         <f t="shared" si="13"/>
-        <v>7.2094519623627146E-2</v>
+        <v>6.9787244849306276E-2</v>
       </c>
     </row>
     <row r="484" spans="8:9">
       <c r="H484">
-        <v>2.21</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="I484" s="55">
         <f t="shared" si="13"/>
-        <v>7.1876875583872596E-2</v>
+        <v>6.9586562448014339E-2</v>
       </c>
     </row>
     <row r="485" spans="8:9">
       <c r="H485">
-        <v>2.2200000000000002</v>
+        <v>2.33</v>
       </c>
       <c r="I485" s="55">
         <f t="shared" si="13"/>
-        <v>7.1660866738472703E-2</v>
+        <v>6.9387316572681504E-2</v>
       </c>
     </row>
     <row r="486" spans="8:9">
       <c r="H486">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="I486" s="55">
         <f t="shared" si="13"/>
-        <v>7.1446473518868236E-2</v>
+        <v>6.91894908409426E-2</v>
       </c>
     </row>
     <row r="487" spans="8:9">
       <c r="H487">
-        <v>2.2400000000000002</v>
+        <v>2.35</v>
       </c>
       <c r="I487" s="55">
         <f t="shared" si="13"/>
-        <v>7.123367667705803E-2</v>
+        <v>6.8993069126225728E-2</v>
       </c>
     </row>
     <row r="488" spans="8:9">
       <c r="H488">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="I488" s="55">
         <f t="shared" si="13"/>
-        <v>7.1022457278945364E-2</v>
+        <v>6.8798035552690887E-2</v>
       </c>
     </row>
     <row r="489" spans="8:9">
       <c r="H489">
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="I489" s="55">
         <f t="shared" si="13"/>
-        <v>7.0812796697851343E-2</v>
+        <v>6.8604374490289111E-2</v>
       </c>
     </row>
     <row r="490" spans="8:9">
       <c r="H490">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="I490" s="55">
         <f t="shared" si="13"/>
-        <v>7.0604676608190434E-2</v>
+        <v>6.8412070549939946E-2</v>
       </c>
     </row>
     <row r="491" spans="8:9">
       <c r="H491">
-        <v>2.2799999999999998</v>
+        <v>2.39</v>
       </c>
       <c r="I491" s="55">
         <f t="shared" si="13"/>
-        <v>7.0398078979303086E-2</v>
+        <v>6.8221108578822798E-2</v>
       </c>
     </row>
     <row r="492" spans="8:9">
       <c r="H492">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="I492" s="55">
         <f t="shared" si="13"/>
-        <v>7.0192986069441285E-2</v>
+        <v>6.8031473655779995E-2</v>
       </c>
     </row>
     <row r="493" spans="8:9">
       <c r="H493">
-        <v>2.2999999999999998</v>
+        <v>2.41</v>
       </c>
       <c r="I493" s="55">
         <f t="shared" si="13"/>
-        <v>6.9989380419902256E-2</v>
+        <v>6.7843151086827647E-2</v>
       </c>
     </row>
     <row r="494" spans="8:9">
       <c r="H494">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="I494" s="55">
         <f t="shared" si="13"/>
-        <v>6.9787244849306276E-2</v>
+        <v>6.7656126400771982E-2</v>
       </c>
     </row>
     <row r="495" spans="8:9">
       <c r="H495">
-        <v>2.3199999999999998</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="I495" s="55">
         <f t="shared" si="13"/>
-        <v>6.9586562448014339E-2</v>
+        <v>6.7470385344927691E-2</v>
       </c>
     </row>
     <row r="496" spans="8:9">
       <c r="H496">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="I496" s="55">
         <f t="shared" si="13"/>
-        <v>6.9387316572681504E-2</v>
+        <v>6.7285913880936132E-2</v>
       </c>
     </row>
     <row r="497" spans="8:9">
       <c r="H497">
-        <v>2.34</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="I497" s="55">
         <f t="shared" si="13"/>
-        <v>6.91894908409426E-2</v>
+        <v>6.7102698180679973E-2</v>
       </c>
     </row>
     <row r="498" spans="8:9">
       <c r="H498">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="I498" s="55">
         <f t="shared" si="13"/>
-        <v>6.8993069126225728E-2</v>
+        <v>6.6920724622292219E-2</v>
       </c>
     </row>
     <row r="499" spans="8:9">
       <c r="H499">
-        <v>2.36</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="I499" s="55">
         <f t="shared" si="13"/>
-        <v>6.8798035552690887E-2</v>
+        <v>6.6739979786256801E-2</v>
       </c>
     </row>
     <row r="500" spans="8:9">
       <c r="H500">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="I500" s="55">
         <f t="shared" si="13"/>
-        <v>6.8604374490289111E-2</v>
+        <v>6.6560450451598294E-2</v>
       </c>
     </row>
     <row r="501" spans="8:9">
       <c r="H501">
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="I501" s="55">
         <f t="shared" si="13"/>
-        <v>6.8412070549939946E-2</v>
+        <v>6.6382123592158546E-2</v>
       </c>
     </row>
     <row r="502" spans="8:9">
       <c r="H502">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="I502" s="55">
         <f t="shared" si="13"/>
-        <v>6.8221108578822798E-2</v>
+        <v>6.6204986372957478E-2</v>
       </c>
     </row>
     <row r="503" spans="8:9">
       <c r="H503">
-        <v>2.4</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="I503" s="55">
         <f t="shared" si="13"/>
-        <v>6.8031473655779995E-2</v>
+        <v>6.6029026146636471E-2</v>
       </c>
     </row>
     <row r="504" spans="8:9">
       <c r="H504">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="I504" s="55">
         <f t="shared" si="13"/>
-        <v>6.7843151086827647E-2</v>
+        <v>6.5854230449981385E-2</v>
       </c>
     </row>
     <row r="505" spans="8:9">
       <c r="H505">
-        <v>2.42</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="I505" s="55">
         <f t="shared" si="13"/>
-        <v>6.7656126400771982E-2</v>
+        <v>6.5680587000523913E-2</v>
       </c>
     </row>
     <row r="506" spans="8:9">
       <c r="H506">
-        <v>2.4300000000000002</v>
+        <v>2.54</v>
       </c>
       <c r="I506" s="55">
         <f t="shared" si="13"/>
-        <v>6.7470385344927691E-2</v>
+        <v>6.5508083693218408E-2</v>
       </c>
     </row>
     <row r="507" spans="8:9">
       <c r="H507">
-        <v>2.44</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I507" s="55">
         <f t="shared" si="13"/>
-        <v>6.7285913880936132E-2</v>
+        <v>6.5336708597192955E-2</v>
       </c>
     </row>
     <row r="508" spans="8:9">
       <c r="H508">
-        <v>2.4500000000000002</v>
+        <v>2.56</v>
       </c>
       <c r="I508" s="55">
         <f t="shared" si="13"/>
-        <v>6.7102698180679973E-2</v>
+        <v>6.5166449952572161E-2</v>
       </c>
     </row>
     <row r="509" spans="8:9">
       <c r="H509">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="I509" s="55">
         <f t="shared" si="13"/>
-        <v>6.6920724622292219E-2</v>
+        <v>6.4997296167370169E-2</v>
       </c>
     </row>
     <row r="510" spans="8:9">
       <c r="H510">
-        <v>2.4700000000000002</v>
+        <v>2.58</v>
       </c>
       <c r="I510" s="55">
-        <f t="shared" si="13"/>
-        <v>6.6739979786256801E-2</v>
+        <f t="shared" ref="I510:I552" si="14">IF(H510&lt;$C$253/3,   ($C$254*$C$251/$C$255)*(1+(3*($C$252-1)*H510/$C$253)),   IF(H510&lt;=$C$253,   $C$254*$C$251*$C$252/$C$255,   $C$254*$C$251*$C$252/$C$255*($C$253/H510)^(2/3)   ))</f>
+        <v>6.4829235814451935E-2</v>
       </c>
     </row>
     <row r="511" spans="8:9">
       <c r="H511">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="I511" s="55">
-        <f t="shared" si="13"/>
-        <v>6.6560450451598294E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.4662257628560982E-2</v>
       </c>
     </row>
     <row r="512" spans="8:9">
       <c r="H512">
-        <v>2.4900000000000002</v>
+        <v>2.6</v>
       </c>
       <c r="I512" s="55">
-        <f t="shared" si="13"/>
-        <v>6.6382123592158546E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.449635050341207E-2</v>
       </c>
     </row>
     <row r="513" spans="8:9">
       <c r="H513">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="I513" s="55">
-        <f t="shared" si="13"/>
-        <v>6.6204986372957478E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.4331503488846975E-2</v>
       </c>
     </row>
     <row r="514" spans="8:9">
       <c r="H514">
-        <v>2.5099999999999998</v>
+        <v>2.62</v>
       </c>
       <c r="I514" s="55">
-        <f t="shared" si="13"/>
-        <v>6.6029026146636471E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.4167705788051782E-2</v>
       </c>
     </row>
     <row r="515" spans="8:9">
       <c r="H515">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="I515" s="55">
-        <f t="shared" si="13"/>
-        <v>6.5854230449981385E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.4004946754834202E-2</v>
       </c>
     </row>
     <row r="516" spans="8:9">
       <c r="H516">
-        <v>2.5299999999999998</v>
+        <v>2.64</v>
       </c>
       <c r="I516" s="55">
-        <f t="shared" si="13"/>
-        <v>6.5680587000523913E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.3843215890959426E-2</v>
       </c>
     </row>
     <row r="517" spans="8:9">
       <c r="H517">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="I517" s="55">
-        <f t="shared" si="13"/>
-        <v>6.5508083693218408E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.3682502843542974E-2</v>
       </c>
     </row>
     <row r="518" spans="8:9">
       <c r="H518">
-        <v>2.5499999999999998</v>
+        <v>2.66</v>
       </c>
       <c r="I518" s="55">
-        <f t="shared" si="13"/>
-        <v>6.5336708597192955E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.3522797402498971E-2</v>
       </c>
     </row>
     <row r="519" spans="8:9">
       <c r="H519">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="I519" s="55">
-        <f t="shared" si="13"/>
-        <v>6.5166449952572161E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.3364089498042855E-2</v>
       </c>
     </row>
     <row r="520" spans="8:9">
       <c r="H520">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="I520" s="55">
-        <f t="shared" si="13"/>
-        <v>6.4997296167370169E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.3206369198246654E-2</v>
       </c>
     </row>
     <row r="521" spans="8:9">
       <c r="H521">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="I521" s="55">
-        <f t="shared" ref="I521:I563" si="14">IF(H521&lt;$C$264/3,   ($C$265*$C$262/$C$266)*(1+(3*($C$263-1)*H521/$C$264)),   IF(H521&lt;=$C$264,   $C$265*$C$262*$C$263/$C$266,   $C$265*$C$262*$C$263/$C$266*($C$264/H521)^(2/3)   ))</f>
-        <v>6.4829235814451935E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.30496267066461E-2</v>
       </c>
     </row>
     <row r="522" spans="8:9">
       <c r="H522">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="I522" s="55">
         <f t="shared" si="14"/>
-        <v>6.4662257628560982E-2</v>
+        <v>6.2893852359897653E-2</v>
       </c>
     </row>
     <row r="523" spans="8:9">
       <c r="H523">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="I523" s="55">
         <f t="shared" si="14"/>
-        <v>6.449635050341207E-2</v>
+        <v>6.2739036625484884E-2</v>
       </c>
     </row>
     <row r="524" spans="8:9">
       <c r="H524">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="I524" s="55">
         <f t="shared" si="14"/>
-        <v>6.4331503488846975E-2</v>
+        <v>6.2585170099472384E-2</v>
       </c>
     </row>
     <row r="525" spans="8:9">
       <c r="H525">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="I525" s="55">
         <f t="shared" si="14"/>
-        <v>6.4167705788051782E-2</v>
+        <v>6.2432243504306546E-2</v>
       </c>
     </row>
     <row r="526" spans="8:9">
       <c r="H526">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="I526" s="55">
         <f t="shared" si="14"/>
-        <v>6.4004946754834202E-2</v>
+        <v>6.2280247686661676E-2</v>
       </c>
     </row>
     <row r="527" spans="8:9">
       <c r="H527">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="I527" s="55">
         <f t="shared" si="14"/>
-        <v>6.3843215890959426E-2</v>
+        <v>6.2129173615330699E-2</v>
       </c>
     </row>
     <row r="528" spans="8:9">
       <c r="H528">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="I528" s="55">
         <f t="shared" si="14"/>
-        <v>6.3682502843542974E-2</v>
+        <v>6.1979012379158996E-2</v>
       </c>
     </row>
     <row r="529" spans="8:9">
       <c r="H529">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="I529" s="55">
         <f t="shared" si="14"/>
-        <v>6.3522797402498971E-2</v>
+        <v>6.18297551850207E-2</v>
       </c>
     </row>
     <row r="530" spans="8:9">
       <c r="H530">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="I530" s="55">
         <f t="shared" si="14"/>
-        <v>6.3364089498042855E-2</v>
+        <v>6.1681393355836216E-2</v>
       </c>
     </row>
     <row r="531" spans="8:9">
       <c r="H531">
-        <v>2.68</v>
+        <v>2.79</v>
       </c>
       <c r="I531" s="55">
         <f t="shared" si="14"/>
-        <v>6.3206369198246654E-2</v>
+        <v>6.153391832862997E-2</v>
       </c>
     </row>
     <row r="532" spans="8:9">
       <c r="H532">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="I532" s="55">
         <f t="shared" si="14"/>
-        <v>6.30496267066461E-2</v>
+        <v>6.1387321652627579E-2</v>
       </c>
     </row>
     <row r="533" spans="8:9">
       <c r="H533">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="I533" s="55">
         <f t="shared" si="14"/>
-        <v>6.2893852359897653E-2</v>
+        <v>6.1241594987391366E-2</v>
       </c>
     </row>
     <row r="534" spans="8:9">
       <c r="H534">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="I534" s="55">
         <f t="shared" si="14"/>
-        <v>6.2739036625484884E-2</v>
+        <v>6.1096730100993361E-2</v>
       </c>
     </row>
     <row r="535" spans="8:9">
       <c r="H535">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="I535" s="55">
         <f t="shared" si="14"/>
-        <v>6.2585170099472384E-2</v>
+        <v>6.0952718868224912E-2</v>
       </c>
     </row>
     <row r="536" spans="8:9">
       <c r="H536">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="I536" s="55">
         <f t="shared" si="14"/>
-        <v>6.2432243504306546E-2</v>
+        <v>6.0809553268842097E-2</v>
       </c>
     </row>
     <row r="537" spans="8:9">
       <c r="H537">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="I537" s="55">
         <f t="shared" si="14"/>
-        <v>6.2280247686661676E-2</v>
+        <v>6.0667225385845965E-2</v>
       </c>
     </row>
     <row r="538" spans="8:9">
       <c r="H538">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="I538" s="55">
         <f t="shared" si="14"/>
-        <v>6.2129173615330699E-2</v>
+        <v>6.0525727403796865E-2</v>
       </c>
     </row>
     <row r="539" spans="8:9">
       <c r="H539">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="I539" s="55">
         <f t="shared" si="14"/>
-        <v>6.1979012379158996E-2</v>
+        <v>6.0385051607162142E-2</v>
       </c>
     </row>
     <row r="540" spans="8:9">
       <c r="H540">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="I540" s="55">
         <f t="shared" si="14"/>
-        <v>6.18297551850207E-2</v>
+        <v>6.0245190378696391E-2</v>
       </c>
     </row>
     <row r="541" spans="8:9">
       <c r="H541">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="I541" s="55">
         <f t="shared" si="14"/>
-        <v>6.1681393355836216E-2</v>
+        <v>6.0106136197853308E-2</v>
       </c>
     </row>
     <row r="542" spans="8:9">
       <c r="H542">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="I542" s="55">
         <f t="shared" si="14"/>
-        <v>6.153391832862997E-2</v>
+        <v>5.9967881639228844E-2</v>
       </c>
     </row>
     <row r="543" spans="8:9">
       <c r="H543">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="I543" s="55">
         <f t="shared" si="14"/>
-        <v>6.1387321652627579E-2</v>
+        <v>5.9830419371034442E-2</v>
       </c>
     </row>
     <row r="544" spans="8:9">
       <c r="H544">
-        <v>2.81</v>
+        <v>2.92</v>
       </c>
       <c r="I544" s="55">
         <f t="shared" si="14"/>
-        <v>6.1241594987391366E-2</v>
+        <v>5.9693742153600148E-2</v>
       </c>
     </row>
     <row r="545" spans="8:9">
       <c r="H545">
-        <v>2.82</v>
+        <v>2.93</v>
       </c>
       <c r="I545" s="55">
         <f t="shared" si="14"/>
-        <v>6.1096730100993361E-2</v>
+        <v>5.9557842837906549E-2</v>
       </c>
     </row>
     <row r="546" spans="8:9">
       <c r="H546">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="I546" s="55">
         <f t="shared" si="14"/>
-        <v>6.0952718868224912E-2</v>
+        <v>5.9422714364145E-2</v>
       </c>
     </row>
     <row r="547" spans="8:9">
       <c r="H547">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="I547" s="55">
         <f t="shared" si="14"/>
-        <v>6.0809553268842097E-2</v>
+        <v>5.9288349760305649E-2</v>
       </c>
     </row>
     <row r="548" spans="8:9">
       <c r="H548">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="I548" s="55">
         <f t="shared" si="14"/>
-        <v>6.0667225385845965E-2</v>
+        <v>5.9154742140792402E-2</v>
       </c>
     </row>
     <row r="549" spans="8:9">
       <c r="H549">
-        <v>2.86</v>
+        <v>2.97</v>
       </c>
       <c r="I549" s="55">
         <f t="shared" si="14"/>
-        <v>6.0525727403796865E-2</v>
+        <v>5.9021884705064413E-2</v>
       </c>
     </row>
     <row r="550" spans="8:9">
       <c r="H550">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="I550" s="55">
         <f t="shared" si="14"/>
-        <v>6.0385051607162142E-2</v>
+        <v>5.8889770736303346E-2</v>
       </c>
     </row>
     <row r="551" spans="8:9">
       <c r="H551">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="I551" s="55">
         <f t="shared" si="14"/>
-        <v>6.0245190378696391E-2</v>
+        <v>5.8758393600105874E-2</v>
       </c>
     </row>
     <row r="552" spans="8:9">
       <c r="H552">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="I552" s="55">
-        <f t="shared" si="14"/>
-        <v>6.0106136197853308E-2</v>
-      </c>
-    </row>
-    <row r="553" spans="8:9">
-      <c r="H553">
-        <v>2.9</v>
-      </c>
-      <c r="I553" s="55">
-        <f t="shared" si="14"/>
-        <v>5.9967881639228844E-2</v>
-      </c>
-    </row>
-    <row r="554" spans="8:9">
-      <c r="H554">
-        <v>2.91</v>
-      </c>
-      <c r="I554" s="55">
-        <f t="shared" si="14"/>
-        <v>5.9830419371034442E-2</v>
-      </c>
-    </row>
-    <row r="555" spans="8:9">
-      <c r="H555">
-        <v>2.92</v>
-      </c>
-      <c r="I555" s="55">
-        <f t="shared" si="14"/>
-        <v>5.9693742153600148E-2</v>
-      </c>
-    </row>
-    <row r="556" spans="8:9">
-      <c r="H556">
-        <v>2.93</v>
-      </c>
-      <c r="I556" s="55">
-        <f t="shared" si="14"/>
-        <v>5.9557842837906549E-2</v>
-      </c>
-    </row>
-    <row r="557" spans="8:9">
-      <c r="H557">
-        <v>2.94</v>
-      </c>
-      <c r="I557" s="55">
-        <f t="shared" si="14"/>
-        <v>5.9422714364145E-2</v>
-      </c>
-    </row>
-    <row r="558" spans="8:9">
-      <c r="H558">
-        <v>2.95</v>
-      </c>
-      <c r="I558" s="55">
-        <f t="shared" si="14"/>
-        <v>5.9288349760305649E-2</v>
-      </c>
-    </row>
-    <row r="559" spans="8:9">
-      <c r="H559">
-        <v>2.96</v>
-      </c>
-      <c r="I559" s="55">
-        <f t="shared" si="14"/>
-        <v>5.9154742140792402E-2</v>
-      </c>
-    </row>
-    <row r="560" spans="8:9">
-      <c r="H560">
-        <v>2.97</v>
-      </c>
-      <c r="I560" s="55">
-        <f t="shared" si="14"/>
-        <v>5.9021884705064413E-2</v>
-      </c>
-    </row>
-    <row r="561" spans="8:9">
-      <c r="H561">
-        <v>2.98</v>
-      </c>
-      <c r="I561" s="55">
-        <f t="shared" si="14"/>
-        <v>5.8889770736303346E-2</v>
-      </c>
-    </row>
-    <row r="562" spans="8:9">
-      <c r="H562">
-        <v>2.99</v>
-      </c>
-      <c r="I562" s="55">
-        <f t="shared" si="14"/>
-        <v>5.8758393600105874E-2</v>
-      </c>
-    </row>
-    <row r="563" spans="8:9">
-      <c r="H563">
-        <v>3</v>
-      </c>
-      <c r="I563" s="55">
         <f t="shared" si="14"/>
         <v>5.8627746743201051E-2</v>
       </c>
@@ -19193,11 +18764,11 @@
     <mergeCell ref="AL8:AM8"/>
     <mergeCell ref="AL9:AM9"/>
     <mergeCell ref="F127:G127"/>
-    <mergeCell ref="K246:L246"/>
+    <mergeCell ref="K235:L235"/>
     <mergeCell ref="B173:L173"/>
     <mergeCell ref="E174:G174"/>
     <mergeCell ref="K174:L174"/>
-    <mergeCell ref="H232:J232"/>
+    <mergeCell ref="H221:J221"/>
     <mergeCell ref="C10:E10"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
